--- a/database/event/8063/event_8063_evp_summary.xlsx
+++ b/database/event/8063/event_8063_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.0423</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.1099</v>
       </c>
       <c r="D2" t="n">
         <v>3.6355</v>
@@ -545,7 +545,7 @@
         <v>5.9418</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.2484</v>
       </c>
       <c r="D3" t="n">
         <v>1.979</v>
@@ -591,7 +591,7 @@
         <v>4.7916</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1.0067</v>
       </c>
       <c r="D4" t="n">
         <v>1.5143</v>
@@ -637,7 +637,7 @@
         <v>4.6914</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.9857</v>
       </c>
       <c r="D5" t="n">
         <v>1.4739</v>
@@ -683,7 +683,7 @@
         <v>4.469</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.9389</v>
       </c>
       <c r="D6" t="n">
         <v>1.384</v>
@@ -729,7 +729,7 @@
         <v>4.2445</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.8918</v>
       </c>
       <c r="D7" t="n">
         <v>1.2933</v>
@@ -775,7 +775,7 @@
         <v>3.9932</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.839</v>
       </c>
       <c r="D8" t="n">
         <v>1.1918</v>
@@ -821,7 +821,7 @@
         <v>3.833</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.8053</v>
       </c>
       <c r="D9" t="n">
         <v>1.1271</v>
@@ -867,7 +867,7 @@
         <v>3.6668</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.7704</v>
       </c>
       <c r="D10" t="n">
         <v>1.0599</v>
@@ -913,7 +913,7 @@
         <v>3.5357</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.7429</v>
       </c>
       <c r="D11" t="n">
         <v>1.007</v>
@@ -959,7 +959,7 @@
         <v>3.2343</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.6795</v>
       </c>
       <c r="D12" t="n">
         <v>0.8852</v>
@@ -1005,7 +1005,7 @@
         <v>3.2135</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.6752</v>
       </c>
       <c r="D13" t="n">
         <v>0.8768</v>
@@ -1051,7 +1051,7 @@
         <v>3.0427</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.6393</v>
       </c>
       <c r="D14" t="n">
         <v>0.8078</v>
@@ -1097,7 +1097,7 @@
         <v>2.9526</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.6203</v>
       </c>
       <c r="D15" t="n">
         <v>0.7714</v>
@@ -1143,7 +1143,7 @@
         <v>2.859</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.6007</v>
       </c>
       <c r="D16" t="n">
         <v>0.7336</v>
@@ -1189,7 +1189,7 @@
         <v>2.8441</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.5976</v>
       </c>
       <c r="D17" t="n">
         <v>0.7276</v>
@@ -1235,7 +1235,7 @@
         <v>2.657</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5582</v>
       </c>
       <c r="D18" t="n">
         <v>0.652</v>
@@ -1281,7 +1281,7 @@
         <v>2.2319</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.4689</v>
       </c>
       <c r="D19" t="n">
         <v>0.4803</v>
@@ -1327,7 +1327,7 @@
         <v>2.1965</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.4615</v>
       </c>
       <c r="D20" t="n">
         <v>0.466</v>
@@ -1373,7 +1373,7 @@
         <v>2.0309</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.4267</v>
       </c>
       <c r="D21" t="n">
         <v>0.3991</v>
@@ -1419,7 +1419,7 @@
         <v>1.9989</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="D22" t="n">
         <v>0.3861</v>
@@ -1465,7 +1465,7 @@
         <v>1.9931</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.4188</v>
       </c>
       <c r="D23" t="n">
         <v>0.3838</v>
@@ -1511,7 +1511,7 @@
         <v>1.7389</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.3653</v>
       </c>
       <c r="D24" t="n">
         <v>0.2811</v>
@@ -1557,7 +1557,7 @@
         <v>1.6915</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.3554</v>
       </c>
       <c r="D25" t="n">
         <v>0.262</v>
@@ -1603,7 +1603,7 @@
         <v>1.6502</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.3467</v>
       </c>
       <c r="D26" t="n">
         <v>0.2453</v>
@@ -1649,7 +1649,7 @@
         <v>1.5414</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.3239</v>
       </c>
       <c r="D27" t="n">
         <v>0.2013</v>
@@ -1695,7 +1695,7 @@
         <v>1.5068</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.3166</v>
       </c>
       <c r="D28" t="n">
         <v>0.1874</v>
@@ -1741,7 +1741,7 @@
         <v>1.4861</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.3122</v>
       </c>
       <c r="D29" t="n">
         <v>0.179</v>
@@ -1787,7 +1787,7 @@
         <v>1.4718</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.3092</v>
       </c>
       <c r="D30" t="n">
         <v>0.1732</v>
@@ -1833,7 +1833,7 @@
         <v>1.4611</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="D31" t="n">
         <v>0.1689</v>
@@ -1879,7 +1879,7 @@
         <v>1.3994</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="D32" t="n">
         <v>0.144</v>
@@ -1925,7 +1925,7 @@
         <v>1.166</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="D33" t="n">
         <v>0.0497</v>
@@ -1971,7 +1971,7 @@
         <v>1.1345</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.2384</v>
       </c>
       <c r="D34" t="n">
         <v>0.037</v>
@@ -2017,7 +2017,7 @@
         <v>1.0639</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2235</v>
       </c>
       <c r="D35" t="n">
         <v>0.008399999999999999</v>
@@ -2063,7 +2063,7 @@
         <v>0.8667</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.1821</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0712</v>
@@ -2109,7 +2109,7 @@
         <v>0.7607</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.1598</v>
       </c>
       <c r="D37" t="n">
         <v>-0.1141</v>
@@ -2155,7 +2155,7 @@
         <v>0.7023</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.1476</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1376</v>
@@ -2201,7 +2201,7 @@
         <v>0.5834</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1226</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1857</v>
@@ -2247,7 +2247,7 @@
         <v>0.5489000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.1153</v>
       </c>
       <c r="D40" t="n">
         <v>-0.1996</v>
@@ -2293,7 +2293,7 @@
         <v>0.5219</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2105</v>
@@ -2339,7 +2339,7 @@
         <v>0.5056</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.1062</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2171</v>
@@ -2385,7 +2385,7 @@
         <v>0.5034</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1058</v>
       </c>
       <c r="D43" t="n">
         <v>-0.218</v>
@@ -2431,7 +2431,7 @@
         <v>0.4584</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0963</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2362</v>
@@ -2477,7 +2477,7 @@
         <v>0.3598</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.0756</v>
       </c>
       <c r="D45" t="n">
         <v>-0.276</v>
@@ -2523,7 +2523,7 @@
         <v>0.3096</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2963</v>
@@ -2569,7 +2569,7 @@
         <v>0.3009</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2998</v>
@@ -2615,7 +2615,7 @@
         <v>0.268</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3131</v>
@@ -2661,7 +2661,7 @@
         <v>0.2321</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0488</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3276</v>
@@ -2707,7 +2707,7 @@
         <v>0.1574</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0331</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3578</v>
@@ -2753,7 +2753,7 @@
         <v>0.0487</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.0102</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4017</v>
@@ -2799,7 +2799,7 @@
         <v>0.0482</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.0101</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4019</v>
@@ -2845,7 +2845,7 @@
         <v>-0.0129</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0027</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4266</v>
@@ -2891,7 +2891,7 @@
         <v>-0.0364</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.0076</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4361</v>
@@ -2937,7 +2937,7 @@
         <v>-0.1082</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.0227</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4651</v>
@@ -2983,7 +2983,7 @@
         <v>-0.1086</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0228</v>
       </c>
       <c r="D56" t="n">
         <v>-0.4652</v>
@@ -3029,7 +3029,7 @@
         <v>-0.143</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.03</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4791</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3094</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.065</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5464</v>
@@ -3121,7 +3121,7 @@
         <v>-0.3253</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.0683</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5528</v>
@@ -3167,7 +3167,7 @@
         <v>-0.3304</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.0694</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5548</v>
@@ -3213,7 +3213,7 @@
         <v>-0.3459</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.0727</v>
       </c>
       <c r="D61" t="n">
         <v>-0.5611</v>
@@ -3259,7 +3259,7 @@
         <v>-0.449</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6027</v>
@@ -3305,7 +3305,7 @@
         <v>-0.4637</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.0974</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6087</v>
@@ -3351,7 +3351,7 @@
         <v>-0.6521</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.137</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6848</v>
@@ -3397,7 +3397,7 @@
         <v>-0.7927</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.1665</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7416</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8339</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.1752</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7582</v>
@@ -3489,7 +3489,7 @@
         <v>-0.8646</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.1817</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7706</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9292</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.1952</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7967</v>
@@ -3581,7 +3581,7 @@
         <v>-1.0103</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.2123</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8295</v>
@@ -3627,7 +3627,7 @@
         <v>-1.1783</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.2476</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8974</v>
@@ -3673,7 +3673,7 @@
         <v>-1.2912</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.2713</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9429999999999999</v>
@@ -3719,7 +3719,7 @@
         <v>-1.4295</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.3003</v>
       </c>
       <c r="D72" t="n">
         <v>-0.9988</v>
@@ -3765,7 +3765,7 @@
         <v>-1.4295</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.3003</v>
       </c>
       <c r="D73" t="n">
         <v>-0.9988</v>
@@ -3811,7 +3811,7 @@
         <v>-1.4603</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.3068</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0113</v>
@@ -3857,7 +3857,7 @@
         <v>-1.5214</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.3197</v>
       </c>
       <c r="D75" t="n">
         <v>-1.036</v>
@@ -3903,7 +3903,7 @@
         <v>-1.5346</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.3224</v>
       </c>
       <c r="D76" t="n">
         <v>-1.0413</v>
@@ -3949,7 +3949,7 @@
         <v>-1.6345</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.3434</v>
       </c>
       <c r="D77" t="n">
         <v>-1.0817</v>
@@ -3995,7 +3995,7 @@
         <v>-1.8306</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.3846</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1609</v>
@@ -4041,7 +4041,7 @@
         <v>-1.9907</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.4183</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2256</v>
@@ -4087,7 +4087,7 @@
         <v>-2</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-0.4202</v>
       </c>
       <c r="D80" t="n">
         <v>-1.2293</v>
@@ -4133,7 +4133,7 @@
         <v>-2.0895</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-0.439</v>
       </c>
       <c r="D81" t="n">
         <v>-1.2655</v>
@@ -4179,7 +4179,7 @@
         <v>-2.8528</v>
       </c>
       <c r="C82" t="n">
-        <v>-0</v>
+        <v>-0.5994</v>
       </c>
       <c r="D82" t="n">
         <v>-1.5738</v>

--- a/database/event/8063/event_8063_evp_summary.xlsx
+++ b/database/event/8063/event_8063_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.0423</v>
+        <v>9.991199999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1099</v>
+        <v>2.0992</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6355</v>
+        <v>3.5366</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0423</v>
+        <v>9.991199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4422</v>
+        <v>3.3911</v>
       </c>
       <c r="G2" t="n">
         <v>6.6001</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4422</v>
+        <v>3.3911</v>
       </c>
       <c r="I2" t="n">
         <v>3.5067</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9418</v>
+        <v>5.8673</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2484</v>
+        <v>1.2327</v>
       </c>
       <c r="D3" t="n">
-        <v>1.979</v>
+        <v>1.8936</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9418</v>
+        <v>5.8673</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0235</v>
+        <v>3.949</v>
       </c>
       <c r="G3" t="n">
         <v>1.9183</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0235</v>
+        <v>3.949</v>
       </c>
       <c r="I3" t="n">
         <v>4.118</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7916</v>
+        <v>4.7558</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0067</v>
+        <v>0.9992</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5143</v>
+        <v>1.4508</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7916</v>
+        <v>4.7558</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9333</v>
+        <v>1.8975</v>
       </c>
       <c r="G4" t="n">
         <v>2.8583</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9333</v>
+        <v>1.8975</v>
       </c>
       <c r="I4" t="n">
         <v>1.9787</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6914</v>
+        <v>4.6614</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9857</v>
+        <v>0.9794</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4739</v>
+        <v>1.4132</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6914</v>
+        <v>4.6614</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6193</v>
+        <v>1.5893</v>
       </c>
       <c r="G5" t="n">
         <v>3.0721</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6193</v>
+        <v>1.5893</v>
       </c>
       <c r="I5" t="n">
         <v>1.6573</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.469</v>
+        <v>4.4091</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9389</v>
+        <v>0.9264</v>
       </c>
       <c r="D6" t="n">
-        <v>1.384</v>
+        <v>1.3127</v>
       </c>
       <c r="E6" t="n">
-        <v>4.469</v>
+        <v>4.4091</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2384</v>
+        <v>3.1785</v>
       </c>
       <c r="G6" t="n">
         <v>1.2306</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2384</v>
+        <v>3.1785</v>
       </c>
       <c r="I6" t="n">
         <v>3.3145</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2445</v>
+        <v>4.2296</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8918</v>
+        <v>0.8887</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2933</v>
+        <v>1.2412</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2445</v>
+        <v>4.2296</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0057</v>
+        <v>0.9908</v>
       </c>
       <c r="G7" t="n">
         <v>3.2388</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0057</v>
+        <v>0.9908</v>
       </c>
       <c r="I7" t="n">
         <v>1.0246</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9932</v>
+        <v>3.9557</v>
       </c>
       <c r="C8" t="n">
-        <v>0.839</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1918</v>
+        <v>1.132</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9932</v>
+        <v>3.9557</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0247</v>
+        <v>1.9872</v>
       </c>
       <c r="G8" t="n">
         <v>1.9685</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0247</v>
+        <v>1.9872</v>
       </c>
       <c r="I8" t="n">
         <v>2.0722</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.833</v>
+        <v>3.7976</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8053</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1271</v>
+        <v>1.0691</v>
       </c>
       <c r="E9" t="n">
-        <v>3.833</v>
+        <v>3.7976</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3889</v>
+        <v>2.3535</v>
       </c>
       <c r="G9" t="n">
         <v>1.4441</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3889</v>
+        <v>2.3535</v>
       </c>
       <c r="I9" t="n">
         <v>2.4337</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6668</v>
+        <v>3.6259</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7704</v>
+        <v>0.7618</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0599</v>
+        <v>1.0006</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6668</v>
+        <v>3.6259</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6668</v>
+        <v>3.6259</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6668</v>
+        <v>3.6259</v>
       </c>
       <c r="I10" t="n">
         <v>3.7182</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5357</v>
+        <v>3.4868</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7429</v>
+        <v>0.7326</v>
       </c>
       <c r="D11" t="n">
-        <v>1.007</v>
+        <v>0.9452</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5357</v>
+        <v>3.4868</v>
       </c>
       <c r="F11" t="n">
-        <v>3.2963</v>
+        <v>3.2474</v>
       </c>
       <c r="G11" t="n">
         <v>0.2394</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2963</v>
+        <v>3.2474</v>
       </c>
       <c r="I11" t="n">
         <v>3.3581</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2343</v>
+        <v>3.2064</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6795</v>
+        <v>0.6737</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8852</v>
+        <v>0.8335</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2343</v>
+        <v>3.2064</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8791</v>
+        <v>1.8512</v>
       </c>
       <c r="G12" t="n">
         <v>1.3552</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8791</v>
+        <v>1.8512</v>
       </c>
       <c r="I12" t="n">
         <v>1.9143</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2135</v>
+        <v>3.1693</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6752</v>
+        <v>0.6659</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8768</v>
+        <v>0.8187</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2135</v>
+        <v>3.1693</v>
       </c>
       <c r="F13" t="n">
-        <v>2.387</v>
+        <v>2.3428</v>
       </c>
       <c r="G13" t="n">
         <v>0.8265</v>
       </c>
       <c r="H13" t="n">
-        <v>2.387</v>
+        <v>2.3428</v>
       </c>
       <c r="I13" t="n">
         <v>2.4431</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0427</v>
+        <v>2.9993</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6393</v>
+        <v>0.6302</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8078</v>
+        <v>0.751</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0427</v>
+        <v>2.9993</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9253</v>
+        <v>2.8819</v>
       </c>
       <c r="G14" t="n">
         <v>0.1174</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9253</v>
+        <v>2.8819</v>
       </c>
       <c r="I14" t="n">
         <v>2.9802</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9526</v>
+        <v>2.9088</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6203</v>
+        <v>0.6111</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7714</v>
+        <v>0.715</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9526</v>
+        <v>2.9088</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9526</v>
+        <v>2.9088</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9526</v>
+        <v>2.9088</v>
       </c>
       <c r="I15" t="n">
         <v>3.008</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.859</v>
+        <v>2.8424</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6007</v>
+        <v>0.5972</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7336</v>
+        <v>0.6885</v>
       </c>
       <c r="E16" t="n">
-        <v>2.859</v>
+        <v>2.8424</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1188</v>
+        <v>1.1022</v>
       </c>
       <c r="G16" t="n">
         <v>1.7402</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1188</v>
+        <v>1.1022</v>
       </c>
       <c r="I16" t="n">
         <v>1.1398</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8441</v>
+        <v>2.7939</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5976</v>
+        <v>0.587</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7276</v>
+        <v>0.6692</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8441</v>
+        <v>2.7939</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3836</v>
+        <v>3.3334</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5395</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3836</v>
+        <v>3.3334</v>
       </c>
       <c r="I17" t="n">
         <v>3.447</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.657</v>
+        <v>2.6269</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5582</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.652</v>
+        <v>0.6026</v>
       </c>
       <c r="E18" t="n">
-        <v>2.657</v>
+        <v>2.6269</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6259</v>
+        <v>1.5958</v>
       </c>
       <c r="G18" t="n">
         <v>1.0311</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6259</v>
+        <v>1.5958</v>
       </c>
       <c r="I18" t="n">
         <v>1.6641</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2319</v>
+        <v>2.198</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4689</v>
+        <v>0.4618</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4803</v>
+        <v>0.4318</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2319</v>
+        <v>2.198</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2841</v>
+        <v>2.2502</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0522</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2841</v>
+        <v>2.2502</v>
       </c>
       <c r="I19" t="n">
         <v>2.3269</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1965</v>
+        <v>2.1653</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4615</v>
+        <v>0.4549</v>
       </c>
       <c r="D20" t="n">
-        <v>0.466</v>
+        <v>0.4187</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1965</v>
+        <v>2.1653</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0989</v>
+        <v>2.0677</v>
       </c>
       <c r="G20" t="n">
         <v>0.09760000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0989</v>
+        <v>2.0677</v>
       </c>
       <c r="I20" t="n">
         <v>2.1382</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0309</v>
+        <v>2.0083</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4267</v>
+        <v>0.4219</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3991</v>
+        <v>0.3562</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0309</v>
+        <v>2.0083</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0309</v>
+        <v>2.0083</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0309</v>
+        <v>2.0083</v>
       </c>
       <c r="I21" t="n">
         <v>2.0594</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.9989</v>
+        <v>1.9709</v>
       </c>
       <c r="C22" t="n">
-        <v>0.42</v>
+        <v>0.4141</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3861</v>
+        <v>0.3413</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9989</v>
+        <v>1.9709</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9164</v>
+        <v>1.9709</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0825</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9164</v>
+        <v>1.9709</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9524</v>
+        <v>2.0211</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0825</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0349</v>
+        <v>2.0211</v>
       </c>
       <c r="N22" t="n">
-        <v>186</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.9931</v>
+        <v>1.9705</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4188</v>
+        <v>0.414</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3838</v>
+        <v>0.3411</v>
       </c>
       <c r="E23" t="n">
-        <v>1.9931</v>
+        <v>1.9705</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9931</v>
+        <v>1.888</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0825</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9931</v>
+        <v>1.888</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0211</v>
+        <v>1.9524</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.0825</v>
       </c>
       <c r="K23" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M23" t="n">
-        <v>2.0211</v>
+        <v>2.0349</v>
       </c>
       <c r="N23" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24">
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7389</v>
+        <v>1.7167</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3653</v>
+        <v>0.3607</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2811</v>
+        <v>0.24</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7389</v>
+        <v>1.7167</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4952</v>
+        <v>1.473</v>
       </c>
       <c r="G24" t="n">
         <v>0.2437</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4952</v>
+        <v>1.473</v>
       </c>
       <c r="I24" t="n">
         <v>1.5232</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.6915</v>
+        <v>1.6726</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3554</v>
+        <v>0.3514</v>
       </c>
       <c r="D25" t="n">
-        <v>0.262</v>
+        <v>0.2225</v>
       </c>
       <c r="E25" t="n">
-        <v>1.6915</v>
+        <v>1.6726</v>
       </c>
       <c r="F25" t="n">
-        <v>1.6915</v>
+        <v>1.6726</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6915</v>
+        <v>1.6726</v>
       </c>
       <c r="I25" t="n">
         <v>1.7152</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.6502</v>
+        <v>1.6318</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3467</v>
+        <v>0.3428</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2453</v>
+        <v>0.2062</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6502</v>
+        <v>1.6318</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6502</v>
+        <v>1.6318</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6502</v>
+        <v>1.6318</v>
       </c>
       <c r="I26" t="n">
         <v>1.6734</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.5414</v>
+        <v>1.5347</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3239</v>
+        <v>0.3224</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2013</v>
+        <v>0.1675</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5414</v>
+        <v>1.5347</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4495</v>
+        <v>0.4428</v>
       </c>
       <c r="G27" t="n">
         <v>1.0919</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4495</v>
+        <v>0.4428</v>
       </c>
       <c r="I27" t="n">
         <v>0.4579</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.5068</v>
+        <v>1.4956</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3166</v>
+        <v>0.3142</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1874</v>
+        <v>0.1519</v>
       </c>
       <c r="E28" t="n">
-        <v>1.5068</v>
+        <v>1.4956</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5068</v>
+        <v>1.4956</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5068</v>
+        <v>1.4956</v>
       </c>
       <c r="I28" t="n">
         <v>1.5209</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.4861</v>
+        <v>1.4754</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3122</v>
+        <v>0.31</v>
       </c>
       <c r="D29" t="n">
-        <v>0.179</v>
+        <v>0.1439</v>
       </c>
       <c r="E29" t="n">
-        <v>1.4861</v>
+        <v>1.4754</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7221</v>
+        <v>0.7114</v>
       </c>
       <c r="G29" t="n">
         <v>0.764</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7221</v>
+        <v>0.7114</v>
       </c>
       <c r="I29" t="n">
         <v>0.7356</v>
@@ -1790,7 +1790,7 @@
         <v>0.3092</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1732</v>
+        <v>0.1425</v>
       </c>
       <c r="E30" t="n">
         <v>1.4718</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.4611</v>
+        <v>1.4394</v>
       </c>
       <c r="C31" t="n">
-        <v>0.307</v>
+        <v>0.3024</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1689</v>
+        <v>0.1295</v>
       </c>
       <c r="E31" t="n">
-        <v>1.4611</v>
+        <v>1.4394</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4611</v>
+        <v>1.4394</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4611</v>
+        <v>1.4394</v>
       </c>
       <c r="I31" t="n">
         <v>1.4885</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.3994</v>
+        <v>1.3775</v>
       </c>
       <c r="C32" t="n">
-        <v>0.294</v>
+        <v>0.2894</v>
       </c>
       <c r="D32" t="n">
-        <v>0.144</v>
+        <v>0.1049</v>
       </c>
       <c r="E32" t="n">
-        <v>1.3994</v>
+        <v>1.3775</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4777</v>
+        <v>1.4558</v>
       </c>
       <c r="G32" t="n">
         <v>-0.07829999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4777</v>
+        <v>1.4558</v>
       </c>
       <c r="I32" t="n">
         <v>1.5054</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.166</v>
+        <v>1.1462</v>
       </c>
       <c r="C33" t="n">
-        <v>0.245</v>
+        <v>0.2408</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0497</v>
+        <v>0.0127</v>
       </c>
       <c r="E33" t="n">
-        <v>1.166</v>
+        <v>1.1462</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3297</v>
+        <v>1.3099</v>
       </c>
       <c r="G33" t="n">
         <v>-0.1637</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3297</v>
+        <v>1.3099</v>
       </c>
       <c r="I33" t="n">
         <v>1.3546</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1345</v>
+        <v>1.1218</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2384</v>
+        <v>0.2357</v>
       </c>
       <c r="D34" t="n">
-        <v>0.037</v>
+        <v>0.003</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1345</v>
+        <v>1.1218</v>
       </c>
       <c r="F34" t="n">
-        <v>1.1345</v>
+        <v>1.1218</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.1345</v>
+        <v>1.1218</v>
       </c>
       <c r="I34" t="n">
         <v>1.1504</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0639</v>
+        <v>1.056</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2235</v>
+        <v>0.2219</v>
       </c>
       <c r="D35" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0232</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0639</v>
+        <v>1.056</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0639</v>
+        <v>1.056</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0639</v>
+        <v>1.056</v>
       </c>
       <c r="I35" t="n">
         <v>1.0738</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8667</v>
+        <v>0.857</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1821</v>
+        <v>0.1801</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0712</v>
+        <v>-0.1025</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8667</v>
+        <v>0.857</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8667</v>
+        <v>0.857</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8667</v>
+        <v>0.857</v>
       </c>
       <c r="I36" t="n">
         <v>0.8788</v>
@@ -2112,7 +2112,7 @@
         <v>0.1598</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1141</v>
+        <v>-0.1408</v>
       </c>
       <c r="E37" t="n">
         <v>0.7607</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7023</v>
+        <v>0.6919</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1476</v>
+        <v>0.1454</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1376</v>
+        <v>-0.1683</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7023</v>
+        <v>0.6919</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7023</v>
+        <v>0.6919</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7023</v>
+        <v>0.6919</v>
       </c>
       <c r="I38" t="n">
         <v>0.7155</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5834</v>
+        <v>0.5812</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1226</v>
+        <v>0.1221</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1857</v>
+        <v>-0.2124</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5834</v>
+        <v>0.5812</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5834</v>
+        <v>0.5812</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5834</v>
+        <v>0.5812</v>
       </c>
       <c r="I39" t="n">
         <v>0.5861</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5417</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1153</v>
+        <v>0.1138</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1996</v>
+        <v>-0.2281</v>
       </c>
       <c r="E40" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5417</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4844</v>
+        <v>0.4772</v>
       </c>
       <c r="G40" t="n">
         <v>0.0645</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4844</v>
+        <v>0.4772</v>
       </c>
       <c r="I40" t="n">
         <v>0.4935</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5219</v>
+        <v>0.5161</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1097</v>
+        <v>0.1084</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2105</v>
+        <v>-0.2383</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5219</v>
+        <v>0.5161</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5219</v>
+        <v>0.5161</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5219</v>
+        <v>0.5161</v>
       </c>
       <c r="I41" t="n">
         <v>0.5293</v>
@@ -2342,7 +2342,7 @@
         <v>0.1062</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2171</v>
+        <v>-0.2425</v>
       </c>
       <c r="E42" t="n">
         <v>0.5056</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5034</v>
+        <v>0.4997</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1058</v>
+        <v>0.105</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.218</v>
+        <v>-0.2448</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5034</v>
+        <v>0.4997</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5034</v>
+        <v>0.4997</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5034</v>
+        <v>0.4997</v>
       </c>
       <c r="I43" t="n">
         <v>0.5081</v>
@@ -2434,7 +2434,7 @@
         <v>0.0963</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2362</v>
+        <v>-0.2613</v>
       </c>
       <c r="E44" t="n">
         <v>0.4584</v>
@@ -2480,7 +2480,7 @@
         <v>0.0756</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.276</v>
+        <v>-0.3006</v>
       </c>
       <c r="E45" t="n">
         <v>0.3598</v>
@@ -2516,93 +2516,93 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3096</v>
+        <v>0.3324</v>
       </c>
       <c r="C46" t="n">
-        <v>0.065</v>
+        <v>0.0698</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2963</v>
+        <v>-0.3115</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3096</v>
+        <v>0.3324</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3096</v>
+        <v>-1.6689</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2.0013</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3096</v>
+        <v>-1.6689</v>
       </c>
       <c r="I46" t="n">
-        <v>0.311</v>
+        <v>-1.7403</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2.0013</v>
       </c>
       <c r="K46" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="M46" t="n">
-        <v>0.311</v>
+        <v>0.2610000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>88</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3009</v>
+        <v>0.3084</v>
       </c>
       <c r="C47" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0648</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2998</v>
+        <v>-0.321</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3009</v>
+        <v>0.3084</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.7004</v>
+        <v>0.3084</v>
       </c>
       <c r="G47" t="n">
-        <v>2.0013</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.7004</v>
+        <v>0.3084</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.7403</v>
+        <v>0.311</v>
       </c>
       <c r="J47" t="n">
-        <v>2.0013</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="L47" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2610000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="N47" t="n">
-        <v>324</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.268</v>
+        <v>0.2631</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0563</v>
+        <v>0.0553</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3131</v>
+        <v>-0.3391</v>
       </c>
       <c r="E48" t="n">
-        <v>0.268</v>
+        <v>0.2631</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3294</v>
+        <v>0.3245</v>
       </c>
       <c r="G48" t="n">
         <v>-0.0614</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3294</v>
+        <v>0.3245</v>
       </c>
       <c r="I48" t="n">
         <v>0.3356</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.2321</v>
+        <v>0.2138</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0488</v>
+        <v>0.0449</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3276</v>
+        <v>-0.3587</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2321</v>
+        <v>0.2138</v>
       </c>
       <c r="F49" t="n">
-        <v>1.2321</v>
+        <v>1.2138</v>
       </c>
       <c r="G49" t="n">
         <v>-1</v>
       </c>
       <c r="H49" t="n">
-        <v>1.2321</v>
+        <v>1.2138</v>
       </c>
       <c r="I49" t="n">
         <v>1.2552</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.1574</v>
+        <v>0.1563</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0331</v>
+        <v>0.0328</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3578</v>
+        <v>-0.3816</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1574</v>
+        <v>0.1563</v>
       </c>
       <c r="F50" t="n">
-        <v>0.1574</v>
+        <v>0.1563</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1574</v>
+        <v>0.1563</v>
       </c>
       <c r="I50" t="n">
         <v>0.1589</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.0487</v>
+        <v>0.0483</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0102</v>
+        <v>0.0101</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4017</v>
+        <v>-0.4247</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0487</v>
+        <v>0.0483</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0487</v>
+        <v>0.0483</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0487</v>
+        <v>0.0483</v>
       </c>
       <c r="I51" t="n">
         <v>0.0491</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0482</v>
+        <v>0.0478</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0101</v>
+        <v>0.01</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4019</v>
+        <v>-0.4249</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0482</v>
+        <v>0.0478</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0482</v>
+        <v>0.0478</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0482</v>
+        <v>0.0478</v>
       </c>
       <c r="I52" t="n">
         <v>0.0486</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.0129</v>
+        <v>-0.019</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0027</v>
+        <v>-0.004</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4266</v>
+        <v>-0.4515</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.0129</v>
+        <v>-0.019</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4066</v>
+        <v>0.4005</v>
       </c>
       <c r="G53" t="n">
         <v>-0.4195</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4066</v>
+        <v>0.4005</v>
       </c>
       <c r="I53" t="n">
         <v>0.4142</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0364</v>
+        <v>-0.0467</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0076</v>
+        <v>-0.0098</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4361</v>
+        <v>-0.4625</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0364</v>
+        <v>-0.0467</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6896</v>
+        <v>0.6793</v>
       </c>
       <c r="G54" t="n">
         <v>-0.726</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6896</v>
+        <v>0.6793</v>
       </c>
       <c r="I54" t="n">
         <v>0.7025</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.1082</v>
+        <v>-0.1028</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0227</v>
+        <v>-0.0216</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4651</v>
+        <v>-0.4849</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.1082</v>
+        <v>-0.1028</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2924</v>
+        <v>-0.287</v>
       </c>
       <c r="G55" t="n">
         <v>0.1842</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2924</v>
+        <v>-0.287</v>
       </c>
       <c r="I55" t="n">
         <v>-0.2993</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.1086</v>
+        <v>-0.1218</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0228</v>
+        <v>-0.0256</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4652</v>
+        <v>-0.4924</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1086</v>
+        <v>-0.1218</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8914</v>
+        <v>0.8782</v>
       </c>
       <c r="G56" t="n">
         <v>-1</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8914</v>
+        <v>0.8782</v>
       </c>
       <c r="I56" t="n">
         <v>0.9081</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.143</v>
+        <v>-0.1414</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.03</v>
+        <v>-0.0297</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4791</v>
+        <v>-0.5002</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.143</v>
+        <v>-0.1414</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.143</v>
+        <v>-0.1414</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.143</v>
+        <v>-0.1414</v>
       </c>
       <c r="I57" t="n">
         <v>-0.145</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.3094</v>
+        <v>-0.3082</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.065</v>
+        <v>-0.0648</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5464</v>
+        <v>-0.5667</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3094</v>
+        <v>-0.3082</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.3094</v>
+        <v>-0.3082</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.3094</v>
+        <v>-0.3082</v>
       </c>
       <c r="I58" t="n">
         <v>-0.3108</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.3253</v>
+        <v>-0.3156</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0683</v>
+        <v>-0.0663</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5528</v>
+        <v>-0.5696</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.3253</v>
+        <v>-0.3156</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3253</v>
+        <v>-0.9827</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>0.6671</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3253</v>
+        <v>-0.9827</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3299</v>
+        <v>-1.0162</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.6671</v>
       </c>
       <c r="K59" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.3299</v>
+        <v>-0.3491</v>
       </c>
       <c r="N59" t="n">
-        <v>152</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.3304</v>
+        <v>-0.3217</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0694</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5548</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3304</v>
+        <v>-0.3217</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.3217</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6671</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.3217</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.0162</v>
+        <v>-0.3299</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6671</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L60" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.3491</v>
+        <v>-0.3299</v>
       </c>
       <c r="N60" t="n">
-        <v>238</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61">
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.3459</v>
+        <v>-0.3429</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0727</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5611</v>
+        <v>-0.5805</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.3459</v>
+        <v>-0.3429</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2035</v>
+        <v>-0.2005</v>
       </c>
       <c r="G61" t="n">
         <v>-0.1424</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2035</v>
+        <v>-0.2005</v>
       </c>
       <c r="I61" t="n">
         <v>-0.2073</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.449</v>
+        <v>-0.4541</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0954</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6027</v>
+        <v>-0.6248</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.449</v>
+        <v>-0.4541</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3416</v>
+        <v>0.3365</v>
       </c>
       <c r="G62" t="n">
         <v>-0.7906</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3416</v>
+        <v>0.3365</v>
       </c>
       <c r="I62" t="n">
         <v>0.348</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.4637</v>
+        <v>-0.4671</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0974</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6087</v>
+        <v>-0.63</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4637</v>
+        <v>-0.4671</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2281</v>
+        <v>0.2247</v>
       </c>
       <c r="G63" t="n">
         <v>-0.6918</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2281</v>
+        <v>0.2247</v>
       </c>
       <c r="I63" t="n">
         <v>0.2324</v>
@@ -3354,7 +3354,7 @@
         <v>-0.137</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6848</v>
+        <v>-0.7037</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6521</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7927</v>
+        <v>-0.781</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1665</v>
+        <v>-0.1641</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7416</v>
+        <v>-0.7551</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7927</v>
+        <v>-0.781</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7927</v>
+        <v>-0.781</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7927</v>
+        <v>-0.781</v>
       </c>
       <c r="I65" t="n">
         <v>-0.8076</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8339</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1752</v>
+        <v>-0.1712</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7582</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8339</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.2712</v>
+        <v>-1.2523</v>
       </c>
       <c r="G66" t="n">
         <v>0.4373</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.2712</v>
+        <v>-1.2523</v>
       </c>
       <c r="I66" t="n">
         <v>-1.295</v>
@@ -3492,7 +3492,7 @@
         <v>-0.1817</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7706</v>
+        <v>-0.7884</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8646</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9292</v>
+        <v>-0.9223</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1952</v>
+        <v>-0.1938</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7967</v>
+        <v>-0.8114</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9292</v>
+        <v>-0.9223</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9292</v>
+        <v>-0.9223</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9292</v>
+        <v>-0.9223</v>
       </c>
       <c r="I68" t="n">
         <v>-0.9379</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0103</v>
+        <v>-1.0027</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2123</v>
+        <v>-0.2107</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8295</v>
+        <v>-0.8434</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0103</v>
+        <v>-1.0027</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.0103</v>
+        <v>-1.0027</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.0103</v>
+        <v>-1.0027</v>
       </c>
       <c r="I69" t="n">
         <v>-1.0197</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1783</v>
+        <v>-1.1608</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.2476</v>
+        <v>-0.2439</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8974</v>
+        <v>-0.9064</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1783</v>
+        <v>-1.1608</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1783</v>
+        <v>-1.1608</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1783</v>
+        <v>-1.1608</v>
       </c>
       <c r="I70" t="n">
         <v>-1.2004</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2912</v>
+        <v>-1.2863</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.2713</v>
+        <v>-0.2703</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-0.9564</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2912</v>
+        <v>-1.2863</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2651</v>
+        <v>-0.2602</v>
       </c>
       <c r="G71" t="n">
         <v>-1.0261</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.2651</v>
+        <v>-0.2602</v>
       </c>
       <c r="I71" t="n">
         <v>-0.2713</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.4295</v>
+        <v>-1.4242</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3003</v>
+        <v>-0.2992</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9988</v>
+        <v>-1.0113</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.4295</v>
+        <v>-1.4242</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.4295</v>
+        <v>-1.4242</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.4295</v>
+        <v>-1.4242</v>
       </c>
       <c r="I72" t="n">
         <v>-1.4362</v>
@@ -3768,7 +3768,7 @@
         <v>-0.3003</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9988</v>
+        <v>-1.0134</v>
       </c>
       <c r="E73" t="n">
         <v>-1.4295</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.4603</v>
+        <v>-1.4321</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.3068</v>
+        <v>-0.3009</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0113</v>
+        <v>-1.0145</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.4603</v>
+        <v>-1.4321</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.8996</v>
+        <v>-1.8714</v>
       </c>
       <c r="G74" t="n">
         <v>0.4393</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.8996</v>
+        <v>-1.8714</v>
       </c>
       <c r="I74" t="n">
         <v>-1.9352</v>
@@ -3860,7 +3860,7 @@
         <v>-0.3197</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.036</v>
+        <v>-1.05</v>
       </c>
       <c r="E75" t="n">
         <v>-1.5214</v>
@@ -3906,7 +3906,7 @@
         <v>-0.3224</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0413</v>
+        <v>-1.0553</v>
       </c>
       <c r="E76" t="n">
         <v>-1.5346</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6345</v>
+        <v>-1.6224</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.3434</v>
+        <v>-0.3409</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0817</v>
+        <v>-1.0903</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6345</v>
+        <v>-1.6224</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.6345</v>
+        <v>-1.6224</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.6345</v>
+        <v>-1.6224</v>
       </c>
       <c r="I77" t="n">
         <v>-1.6498</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.8306</v>
+        <v>-1.8142</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.3846</v>
+        <v>-0.3812</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1609</v>
+        <v>-1.1667</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8306</v>
+        <v>-1.8142</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.1032</v>
+        <v>-1.0868</v>
       </c>
       <c r="G78" t="n">
         <v>-0.7274</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.1032</v>
+        <v>-1.0868</v>
       </c>
       <c r="I78" t="n">
         <v>-1.1239</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.4183</v>
+        <v>-0.4167</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2256</v>
+        <v>-1.2341</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="I79" t="n">
         <v>-2</v>
@@ -4090,7 +4090,7 @@
         <v>-0.4202</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E80" t="n">
         <v>-2</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.0895</v>
+        <v>-2.0739</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.439</v>
+        <v>-0.4357</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2655</v>
+        <v>-1.2702</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.0895</v>
+        <v>-2.0739</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.0895</v>
+        <v>-2.0739</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.0895</v>
+        <v>-2.0739</v>
       </c>
       <c r="I81" t="n">
         <v>-2.109</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-2.8528</v>
+        <v>-2.8347</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.5994</v>
+        <v>-0.5956</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.5738</v>
+        <v>-1.5733</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.8528</v>
+        <v>-2.8347</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.2206</v>
+        <v>-1.2025</v>
       </c>
       <c r="G82" t="n">
         <v>-1.6322</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.2206</v>
+        <v>-1.2025</v>
       </c>
       <c r="I82" t="n">
         <v>-1.2435</v>

--- a/database/event/8063/event_8063_evp_summary.xlsx
+++ b/database/event/8063/event_8063_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.6447</v>
+        <v>10.0734</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0264</v>
+        <v>2.1164</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7663</v>
+        <v>3.8857</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6447</v>
+        <v>10.0734</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4539</v>
+        <v>3.4287</v>
       </c>
       <c r="G2" t="n">
         <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8346</v>
+        <v>4.7794</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3525</v>
+        <v>5.2914</v>
       </c>
       <c r="J2" t="n">
-        <v>6.8984</v>
+        <v>6.8978</v>
       </c>
       <c r="K2" t="n">
         <v>114</v>
@@ -529,7 +529,7 @@
         <v>188</v>
       </c>
       <c r="M2" t="n">
-        <v>12.2509</v>
+        <v>12.1892</v>
       </c>
       <c r="N2" t="n">
         <v>302</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4632</v>
+        <v>5.4496</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1478</v>
+        <v>1.145</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8628</v>
+        <v>1.8204</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4632</v>
+        <v>5.4496</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3886</v>
+        <v>3.3873</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0746</v>
+        <v>2.0749</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6916</v>
+        <v>4.6888</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3281</v>
+        <v>5.3249</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0746</v>
+        <v>2.0749</v>
       </c>
       <c r="K3" t="n">
         <v>143</v>
@@ -575,7 +575,7 @@
         <v>181</v>
       </c>
       <c r="M3" t="n">
-        <v>7.4027</v>
+        <v>7.399800000000001</v>
       </c>
       <c r="N3" t="n">
         <v>324</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2915</v>
+        <v>5.2235</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1118</v>
+        <v>1.0975</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7846</v>
+        <v>1.7194</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2915</v>
+        <v>5.2235</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2474</v>
+        <v>2.2447</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0441</v>
+        <v>3.0446</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2474</v>
+        <v>2.2447</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5523</v>
+        <v>2.5492</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0441</v>
+        <v>3.0446</v>
       </c>
       <c r="K4" t="n">
         <v>143</v>
@@ -621,7 +621,7 @@
         <v>181</v>
       </c>
       <c r="M4" t="n">
-        <v>5.596399999999999</v>
+        <v>5.5938</v>
       </c>
       <c r="N4" t="n">
         <v>324</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8294</v>
+        <v>4.9931</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0147</v>
+        <v>1.0491</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5742</v>
+        <v>1.6165</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8294</v>
+        <v>4.9931</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0175</v>
+        <v>2.0172</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8119</v>
+        <v>2.8121</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0175</v>
+        <v>2.0172</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2912</v>
+        <v>2.2908</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8119</v>
+        <v>2.8121</v>
       </c>
       <c r="K5" t="n">
         <v>143</v>
@@ -667,7 +667,7 @@
         <v>181</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1031</v>
+        <v>5.1029</v>
       </c>
       <c r="N5" t="n">
         <v>324</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3078</v>
+        <v>4.4261</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9051</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3368</v>
+        <v>1.3632</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3078</v>
+        <v>4.4261</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3839</v>
+        <v>2.3782</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9239</v>
+        <v>1.9237</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4927</v>
+        <v>2.4802</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8308</v>
+        <v>2.8167</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9239</v>
+        <v>1.9237</v>
       </c>
       <c r="K6" t="n">
         <v>210</v>
@@ -713,7 +713,7 @@
         <v>107</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7547</v>
+        <v>4.7404</v>
       </c>
       <c r="N6" t="n">
         <v>317</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0214</v>
+        <v>4.1148</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8449</v>
+        <v>0.8645</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2064</v>
+        <v>1.2242</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0214</v>
+        <v>4.1148</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0951</v>
+        <v>1.0948</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9263</v>
+        <v>2.9257</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0951</v>
+        <v>1.0948</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2124</v>
+        <v>1.2121</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9263</v>
+        <v>2.9257</v>
       </c>
       <c r="K7" t="n">
         <v>168</v>
@@ -759,7 +759,7 @@
         <v>131</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1387</v>
+        <v>4.1378</v>
       </c>
       <c r="N7" t="n">
         <v>299</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8153</v>
+        <v>3.923</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8016</v>
+        <v>0.8242</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1126</v>
+        <v>1.1385</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8153</v>
+        <v>3.923</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6797</v>
+        <v>2.6795</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1356</v>
+        <v>1.1352</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1401</v>
+        <v>3.1397</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5661</v>
+        <v>3.5656</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1356</v>
+        <v>1.1352</v>
       </c>
       <c r="K8" t="n">
         <v>210</v>
@@ -805,7 +805,7 @@
         <v>107</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7017</v>
+        <v>4.7008</v>
       </c>
       <c r="N8" t="n">
         <v>317</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5656</v>
+        <v>3.6124</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7491</v>
+        <v>0.759</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9989</v>
+        <v>0.9998</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5656</v>
+        <v>3.6124</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7444</v>
+        <v>3.3275</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8212</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2818</v>
+        <v>4.558</v>
       </c>
       <c r="I9" t="n">
-        <v>3.727</v>
+        <v>4.9195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8212</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="L9" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5482</v>
+        <v>4.9195</v>
       </c>
       <c r="N9" t="n">
-        <v>324</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4993</v>
+        <v>3.5882</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7352</v>
+        <v>0.7539</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9687</v>
+        <v>0.989</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4993</v>
+        <v>3.5882</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2024</v>
+        <v>2.7347</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2969</v>
+        <v>0.8112</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2024</v>
+        <v>3.2605</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4383</v>
+        <v>3.7028</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2969</v>
+        <v>0.8112</v>
       </c>
       <c r="K10" t="n">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="L10" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7352</v>
+        <v>4.514</v>
       </c>
       <c r="N10" t="n">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3275</v>
+        <v>3.4769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.7305</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8905</v>
+        <v>0.9392</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3275</v>
+        <v>3.4769</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3275</v>
+        <v>2.212</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.2958</v>
       </c>
       <c r="H11" t="n">
-        <v>4.558</v>
+        <v>2.212</v>
       </c>
       <c r="I11" t="n">
-        <v>4.9195</v>
+        <v>2.449</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.2958</v>
       </c>
       <c r="K11" t="n">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9195</v>
+        <v>3.7448</v>
       </c>
       <c r="N11" t="n">
-        <v>152</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2837</v>
+        <v>3.3373</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6899</v>
+        <v>0.7012</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8706</v>
+        <v>0.8769</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2837</v>
+        <v>3.3373</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.2326</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0837</v>
+        <v>1.0834</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>2.2326</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4985</v>
+        <v>2.5355</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0837</v>
+        <v>1.0834</v>
       </c>
       <c r="K12" t="n">
         <v>210</v>
@@ -989,7 +989,7 @@
         <v>107</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5822</v>
+        <v>3.6189</v>
       </c>
       <c r="N12" t="n">
         <v>317</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1545</v>
+        <v>3.2382</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6804</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8118</v>
+        <v>0.8326</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1545</v>
+        <v>3.2382</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7805</v>
+        <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>1.374</v>
+        <v>1.3736</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7805</v>
+        <v>1.78</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9712</v>
+        <v>1.9707</v>
       </c>
       <c r="J13" t="n">
-        <v>1.374</v>
+        <v>1.3736</v>
       </c>
       <c r="K13" t="n">
         <v>168</v>
@@ -1035,7 +1035,7 @@
         <v>131</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3452</v>
+        <v>3.3443</v>
       </c>
       <c r="N13" t="n">
         <v>299</v>
@@ -1044,311 +1044,311 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0252</v>
+        <v>3.1902</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6356000000000001</v>
+        <v>0.6703</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7529</v>
+        <v>0.8112</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0252</v>
+        <v>3.1902</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6927</v>
+        <v>2.8363</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3325</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1686</v>
+        <v>3.4829</v>
       </c>
       <c r="I14" t="n">
-        <v>3.508</v>
+        <v>3.7591</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3325</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L14" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8405</v>
+        <v>3.7591</v>
       </c>
       <c r="N14" t="n">
-        <v>238</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8388</v>
+        <v>3.1832</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5964</v>
+        <v>0.6688</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6681</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8388</v>
+        <v>3.1832</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8388</v>
+        <v>2.6927</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.3325</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4884</v>
+        <v>3.1686</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7651</v>
+        <v>3.508</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.3325</v>
       </c>
       <c r="K15" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7651</v>
+        <v>3.8405</v>
       </c>
       <c r="N15" t="n">
-        <v>159</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8342</v>
+        <v>3.0879</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5955</v>
+        <v>0.6488</v>
       </c>
       <c r="D16" t="n">
-        <v>0.666</v>
+        <v>0.7655</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8342</v>
+        <v>3.0879</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6267</v>
+        <v>2.5872</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2075</v>
+        <v>0.2192</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0241</v>
+        <v>2.9377</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3481</v>
+        <v>3.2524</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2075</v>
+        <v>0.2192</v>
       </c>
       <c r="K16" t="n">
+        <v>97</v>
+      </c>
+      <c r="L16" t="n">
+        <v>63</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.4716</v>
+      </c>
+      <c r="N16" t="n">
         <v>160</v>
-      </c>
-      <c r="L16" t="n">
-        <v>78</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.5556</v>
-      </c>
-      <c r="N16" t="n">
-        <v>238</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8111</v>
+        <v>2.9891</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5906</v>
+        <v>0.628</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6555</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8111</v>
+        <v>2.9891</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5921</v>
+        <v>2.6267</v>
       </c>
       <c r="G17" t="n">
-        <v>0.219</v>
+        <v>0.2075</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9483</v>
+        <v>3.0241</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2641</v>
+        <v>3.3481</v>
       </c>
       <c r="J17" t="n">
-        <v>0.219</v>
+        <v>0.2075</v>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4831</v>
+        <v>3.5556</v>
       </c>
       <c r="N17" t="n">
-        <v>160</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.807</v>
+        <v>2.9619</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5898</v>
+        <v>0.6223</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6536</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>2.807</v>
+        <v>2.9619</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>2.7486</v>
       </c>
       <c r="G18" t="n">
-        <v>1.607</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2</v>
+        <v>3.2909</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3286</v>
+        <v>3.6435</v>
       </c>
       <c r="J18" t="n">
-        <v>1.607</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>114</v>
+        <v>213</v>
       </c>
       <c r="L18" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9356</v>
+        <v>3.6435</v>
       </c>
       <c r="N18" t="n">
-        <v>302</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7433</v>
+        <v>2.9321</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5764</v>
+        <v>0.616</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6246</v>
+        <v>0.6959</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7433</v>
+        <v>2.9321</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7433</v>
+        <v>2.408</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.2811</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2793</v>
+        <v>2.5455</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6306</v>
+        <v>2.8182</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.2811</v>
       </c>
       <c r="K19" t="n">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6306</v>
+        <v>3.0993</v>
       </c>
       <c r="N19" t="n">
-        <v>213</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.7241</v>
+        <v>2.8516</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5723</v>
+        <v>0.5991</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6159</v>
+        <v>0.6599</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7241</v>
+        <v>2.8516</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6756</v>
+        <v>2.6759</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0485</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>3.131</v>
+        <v>3.1317</v>
       </c>
       <c r="I20" t="n">
-        <v>3.4665</v>
+        <v>3.4672</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0485</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>102</v>
@@ -1357,7 +1357,7 @@
         <v>44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.515</v>
+        <v>3.5333</v>
       </c>
       <c r="N20" t="n">
         <v>146</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6945</v>
+        <v>2.785</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5661</v>
+        <v>0.5851</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6024</v>
+        <v>0.6302</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6945</v>
+        <v>2.785</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4128</v>
+        <v>3.0348</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2817</v>
+        <v>-0.3701</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5559</v>
+        <v>3.9172</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8297</v>
+        <v>4.3369</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2817</v>
+        <v>-0.3701</v>
       </c>
       <c r="K21" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1114</v>
+        <v>3.9668</v>
       </c>
       <c r="N21" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6638</v>
+        <v>2.7354</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5597</v>
+        <v>0.5747</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5884</v>
+        <v>0.608</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6638</v>
+        <v>2.7354</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0345</v>
+        <v>1.2011</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3707</v>
+        <v>1.6351</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9165</v>
+        <v>1.2011</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3361</v>
+        <v>1.3298</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3707</v>
+        <v>1.6351</v>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="L22" t="n">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9654</v>
+        <v>2.9649</v>
       </c>
       <c r="N22" t="n">
-        <v>160</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.3994</v>
+        <v>2.6005</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5041</v>
+        <v>0.5464</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4681</v>
+        <v>0.5478</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3994</v>
+        <v>2.6005</v>
       </c>
       <c r="F23" t="n">
         <v>2.3994</v>
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3741</v>
+        <v>2.5474</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4988</v>
+        <v>0.5352</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4565</v>
+        <v>0.524</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3741</v>
+        <v>2.5474</v>
       </c>
       <c r="F24" t="n">
         <v>2.3741</v>
@@ -1550,231 +1550,231 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.3454</v>
+        <v>2.4122</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4928</v>
+        <v>0.5068</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4435</v>
+        <v>0.4637</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3454</v>
+        <v>2.4122</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1924</v>
+        <v>2.1089</v>
       </c>
       <c r="G25" t="n">
-        <v>1.153</v>
+        <v>0.1292</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1924</v>
+        <v>2.1089</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3201</v>
+        <v>2.3348</v>
       </c>
       <c r="J25" t="n">
-        <v>1.153</v>
+        <v>0.1292</v>
       </c>
       <c r="K25" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="L25" t="n">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>2.4731</v>
+        <v>2.464</v>
       </c>
       <c r="N25" t="n">
-        <v>299</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.2162</v>
+        <v>2.3069</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4656</v>
+        <v>0.4847</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3847</v>
+        <v>0.4166</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2162</v>
+        <v>2.3069</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2162</v>
+        <v>1.192</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.1528</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2162</v>
+        <v>1.192</v>
       </c>
       <c r="I26" t="n">
-        <v>2.392</v>
+        <v>1.3197</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.1528</v>
       </c>
       <c r="K26" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M26" t="n">
-        <v>2.392</v>
+        <v>2.4725</v>
       </c>
       <c r="N26" t="n">
-        <v>159</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2151</v>
+        <v>2.2306</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4654</v>
+        <v>0.4687</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3842</v>
+        <v>0.3825</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2151</v>
+        <v>2.2306</v>
       </c>
       <c r="F27" t="n">
-        <v>2.0859</v>
+        <v>2.2072</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1292</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.0859</v>
+        <v>2.2072</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3094</v>
+        <v>2.3823</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1292</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L27" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.4386</v>
+        <v>2.3823</v>
       </c>
       <c r="N27" t="n">
-        <v>186</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.0784</v>
+        <v>2.1967</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4367</v>
+        <v>0.4615</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3219</v>
+        <v>0.3674</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0784</v>
+        <v>2.1967</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0784</v>
+        <v>1.99</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.0546</v>
       </c>
       <c r="H28" t="n">
-        <v>2.0784</v>
+        <v>1.99</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2433</v>
+        <v>2.2032</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.0546</v>
       </c>
       <c r="K28" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2433</v>
+        <v>2.2578</v>
       </c>
       <c r="N28" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.0451</v>
+        <v>2.1429</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4297</v>
+        <v>0.4502</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3068</v>
+        <v>0.3434</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0451</v>
+        <v>2.1429</v>
       </c>
       <c r="F29" t="n">
-        <v>1.9905</v>
+        <v>2.0502</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0546</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.9905</v>
+        <v>2.0502</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2037</v>
+        <v>2.2128</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0546</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L29" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.2583</v>
+        <v>2.2128</v>
       </c>
       <c r="N29" t="n">
-        <v>186</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7242</v>
+        <v>1.7525</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3623</v>
+        <v>0.3682</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1607</v>
+        <v>0.169</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7242</v>
+        <v>1.7525</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2141</v>
+        <v>2.2137</v>
       </c>
       <c r="G30" t="n">
         <v>-0.4899</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2141</v>
+        <v>2.2137</v>
       </c>
       <c r="I30" t="n">
-        <v>2.4513</v>
+        <v>2.4509</v>
       </c>
       <c r="J30" t="n">
         <v>-0.4899</v>
@@ -1817,7 +1817,7 @@
         <v>42</v>
       </c>
       <c r="M30" t="n">
-        <v>1.9614</v>
+        <v>1.961</v>
       </c>
       <c r="N30" t="n">
         <v>186</v>
@@ -1826,446 +1826,446 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6877</v>
+        <v>1.6116</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3546</v>
+        <v>0.3386</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1441</v>
+        <v>0.106</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6877</v>
+        <v>1.6116</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6877</v>
+        <v>0.9455</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.5762</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6877</v>
+        <v>0.9455</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8685</v>
+        <v>1.0468</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.5762</v>
       </c>
       <c r="K31" t="n">
-        <v>213</v>
+        <v>97</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8685</v>
+        <v>1.623</v>
       </c>
       <c r="N31" t="n">
-        <v>213</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.5209</v>
+        <v>1.6041</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3195</v>
+        <v>0.337</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="E32" t="n">
-        <v>1.5209</v>
+        <v>1.6041</v>
       </c>
       <c r="F32" t="n">
-        <v>0.945</v>
+        <v>1.6879</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5759</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.945</v>
+        <v>1.6879</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0462</v>
+        <v>1.8687</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5759</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="L32" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.6221</v>
+        <v>1.8687</v>
       </c>
       <c r="N32" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.442</v>
+        <v>1.5365</v>
       </c>
       <c r="C33" t="n">
-        <v>0.303</v>
+        <v>0.3228</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0322</v>
+        <v>0.0725</v>
       </c>
       <c r="E33" t="n">
-        <v>1.442</v>
+        <v>1.5365</v>
       </c>
       <c r="F33" t="n">
-        <v>1.442</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
+        <v>1.4158</v>
+      </c>
+      <c r="H33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="n">
-        <v>1.442</v>
-      </c>
       <c r="I33" t="n">
-        <v>1.5564</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>1.4158</v>
+      </c>
+      <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="K33" t="n">
-        <v>152</v>
-      </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="M33" t="n">
-        <v>1.5564</v>
+        <v>1.4158</v>
       </c>
       <c r="N33" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.4162</v>
+        <v>1.5167</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2975</v>
+        <v>0.3187</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0205</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>1.4162</v>
+        <v>1.5167</v>
       </c>
       <c r="F34" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.4162</v>
-      </c>
       <c r="H34" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.5564</v>
+      </c>
+      <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
+        <v>152</v>
+      </c>
+      <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="J34" t="n">
-        <v>1.4162</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>146</v>
-      </c>
       <c r="M34" t="n">
-        <v>1.4162</v>
+        <v>1.5564</v>
       </c>
       <c r="N34" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>susp</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4032</v>
+        <v>1.4636</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2948</v>
+        <v>0.3075</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0146</v>
+        <v>0.0399</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4032</v>
+        <v>1.4636</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4032</v>
+        <v>1.0463</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4032</v>
+        <v>1.0463</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5145</v>
+        <v>1.0733</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.5145</v>
+        <v>1.0733</v>
       </c>
       <c r="N35" t="n">
-        <v>159</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3862</v>
+        <v>1.3344</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2912</v>
+        <v>0.2804</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0068</v>
+        <v>-0.0178</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3862</v>
+        <v>1.3344</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3862</v>
+        <v>1.4232</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.1048</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3862</v>
+        <v>1.4232</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4962</v>
+        <v>1.5757</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.1048</v>
       </c>
       <c r="K36" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4962</v>
+        <v>1.4709</v>
       </c>
       <c r="N36" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3187</v>
+        <v>1.244</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2771</v>
+        <v>0.2614</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0239</v>
+        <v>-0.0582</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3187</v>
+        <v>1.244</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4235</v>
+        <v>1.1108</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.1048</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4235</v>
+        <v>1.1108</v>
       </c>
       <c r="I37" t="n">
-        <v>1.576</v>
+        <v>1.1688</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.1048</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="L37" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4712</v>
+        <v>1.1688</v>
       </c>
       <c r="N37" t="n">
-        <v>186</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.1108</v>
+        <v>1.221</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2334</v>
+        <v>0.2565</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1185</v>
+        <v>-0.0684</v>
       </c>
       <c r="E38" t="n">
-        <v>1.1108</v>
+        <v>1.221</v>
       </c>
       <c r="F38" t="n">
-        <v>1.1108</v>
+        <v>1.3702</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.1108</v>
+        <v>1.3702</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1688</v>
+        <v>1.4789</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>125</v>
+        <v>159</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1688</v>
+        <v>1.4789</v>
       </c>
       <c r="N38" t="n">
-        <v>125</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.0691</v>
+        <v>1.185</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2246</v>
+        <v>0.249</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1375</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>1.0691</v>
+        <v>1.185</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8998</v>
+        <v>1.3095</v>
       </c>
       <c r="G39" t="n">
-        <v>1.9689</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8998</v>
+        <v>1.3095</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0219</v>
+        <v>1.4134</v>
       </c>
       <c r="J39" t="n">
-        <v>1.9689</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="L39" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9470000000000001</v>
+        <v>1.4134</v>
       </c>
       <c r="N39" t="n">
-        <v>324</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0674</v>
+        <v>1.0908</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2243</v>
+        <v>0.2292</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1383</v>
+        <v>-0.1266</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0674</v>
+        <v>1.0908</v>
       </c>
       <c r="F40" t="n">
-        <v>1.0674</v>
+        <v>0.8988</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.0674</v>
+        <v>0.8988</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0674</v>
+        <v>0.8988</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.0674</v>
+        <v>0.8988</v>
       </c>
       <c r="N40" t="n">
         <v>96</v>
@@ -2286,323 +2286,323 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>susp</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.0165</v>
+        <v>1.061</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2136</v>
+        <v>0.2229</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1615</v>
+        <v>-0.1399</v>
       </c>
       <c r="E41" t="n">
-        <v>1.0165</v>
+        <v>1.061</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0165</v>
+        <v>1.0848</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0165</v>
+        <v>1.0848</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0427</v>
+        <v>1.0848</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.0427</v>
+        <v>1.0848</v>
       </c>
       <c r="N41" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9546</v>
+        <v>0.9583</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2006</v>
+        <v>0.2013</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1896</v>
+        <v>-0.1858</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9546</v>
+        <v>0.9583</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9546</v>
+        <v>0.8184</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9546</v>
+        <v>0.8184</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0569</v>
+        <v>0.8184</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0569</v>
+        <v>0.8184</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.899</v>
+        <v>0.9488</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1889</v>
+        <v>0.1993</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.215</v>
+        <v>-0.19</v>
       </c>
       <c r="E43" t="n">
-        <v>0.899</v>
+        <v>0.9488</v>
       </c>
       <c r="F43" t="n">
-        <v>0.899</v>
+        <v>-0.8919</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1.969</v>
       </c>
       <c r="H43" t="n">
-        <v>0.899</v>
+        <v>-0.8919</v>
       </c>
       <c r="I43" t="n">
-        <v>0.899</v>
+        <v>-1.0129</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1.969</v>
       </c>
       <c r="K43" t="n">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="M43" t="n">
-        <v>0.899</v>
+        <v>0.9561000000000002</v>
       </c>
       <c r="N43" t="n">
-        <v>96</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>ChildKing</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8187</v>
+        <v>0.9376</v>
       </c>
       <c r="C44" t="n">
-        <v>0.172</v>
+        <v>0.197</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2515</v>
+        <v>-0.195</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8187</v>
+        <v>0.9376</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8187</v>
+        <v>0.5501</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8187</v>
+        <v>0.5501</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8187</v>
+        <v>0.5501</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8187</v>
+        <v>0.5501</v>
       </c>
       <c r="N44" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6268</v>
+        <v>0.9181</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1317</v>
+        <v>0.1929</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3389</v>
+        <v>-0.2037</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6268</v>
+        <v>0.9181</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9184</v>
+        <v>0.9005</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.2916</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9184</v>
+        <v>0.9005</v>
       </c>
       <c r="I45" t="n">
-        <v>1.0168</v>
+        <v>0.997</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.2916</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="L45" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7251999999999998</v>
+        <v>0.997</v>
       </c>
       <c r="N45" t="n">
-        <v>186</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6194</v>
+        <v>0.8149</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1301</v>
+        <v>0.1712</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3422</v>
+        <v>-0.2498</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6194</v>
+        <v>0.8149</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5874</v>
+        <v>0.512</v>
       </c>
       <c r="G46" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5874</v>
+        <v>0.512</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6503</v>
+        <v>0.5387</v>
       </c>
       <c r="J46" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="L46" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6823</v>
+        <v>0.5387</v>
       </c>
       <c r="N46" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.599</v>
+        <v>0.6641</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1259</v>
+        <v>0.1395</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3515</v>
+        <v>-0.3172</v>
       </c>
       <c r="E47" t="n">
-        <v>0.599</v>
+        <v>0.6641</v>
       </c>
       <c r="F47" t="n">
-        <v>0.599</v>
+        <v>0.588</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="H47" t="n">
-        <v>0.599</v>
+        <v>0.588</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6303</v>
+        <v>0.651</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="K47" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
-        <v>0.6303</v>
+        <v>0.6823</v>
       </c>
       <c r="N47" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48">
@@ -2612,16 +2612,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5935</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1247</v>
+        <v>0.1335</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.354</v>
+        <v>-0.3299</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5935</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="F48" t="n">
         <v>0.4342</v>
@@ -2654,357 +2654,357 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Boombl4</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5501</v>
+        <v>0.6282</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1156</v>
+        <v>0.132</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3738</v>
+        <v>-0.3332</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5501</v>
+        <v>0.6282</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2095</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3406</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2095</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2379</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>0.3406</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="L49" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5785</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>317</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ChildKing</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5501</v>
+        <v>0.5329</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1156</v>
+        <v>0.112</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3738</v>
+        <v>-0.3758</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5501</v>
+        <v>0.5329</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5501</v>
+        <v>0.4422</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5501</v>
+        <v>0.4422</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5501</v>
+        <v>0.4653</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5501</v>
+        <v>0.4653</v>
       </c>
       <c r="N50" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5124</v>
+        <v>0.4799</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1077</v>
+        <v>0.1008</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3909</v>
+        <v>-0.3995</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5124</v>
+        <v>0.4799</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5124</v>
+        <v>0.9181</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.2916</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5124</v>
+        <v>0.9181</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5392</v>
+        <v>1.0165</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.2916</v>
       </c>
       <c r="K51" t="n">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5392</v>
+        <v>0.7248999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>JBa</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4813</v>
+        <v>0.4415</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1011</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4051</v>
+        <v>-0.4166</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4813</v>
+        <v>0.4415</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4813</v>
+        <v>0.4011</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4813</v>
+        <v>0.4011</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5195</v>
+        <v>0.4114</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5195</v>
+        <v>0.4114</v>
       </c>
       <c r="N52" t="n">
-        <v>152</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Boombl4</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4422</v>
+        <v>0.4377</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0929</v>
+        <v>0.092</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4229</v>
+        <v>-0.4183</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4422</v>
+        <v>0.4377</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4422</v>
+        <v>0.209</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.3405</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4422</v>
+        <v>0.209</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4653</v>
+        <v>0.2373</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.3405</v>
       </c>
       <c r="K53" t="n">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4653</v>
+        <v>0.5778000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>125</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4239</v>
+        <v>0.3776</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0891</v>
+        <v>0.0793</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4312</v>
+        <v>-0.4452</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4239</v>
+        <v>0.3776</v>
       </c>
       <c r="F54" t="n">
-        <v>1.2886</v>
+        <v>0.2793</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.8647</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.2886</v>
+        <v>0.2793</v>
       </c>
       <c r="I54" t="n">
-        <v>1.4266</v>
+        <v>0.2939</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.8647</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5619000000000001</v>
+        <v>0.2939</v>
       </c>
       <c r="N54" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JBa</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4029</v>
+        <v>0.2124</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0847</v>
+        <v>0.0446</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4408</v>
+        <v>-0.5189</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4029</v>
+        <v>0.2124</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4029</v>
+        <v>0.4813</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4029</v>
+        <v>0.4813</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4133</v>
+        <v>0.5195</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.4133</v>
+        <v>0.5195</v>
       </c>
       <c r="N55" t="n">
-        <v>88</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2802</v>
+        <v>0.1404</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0589</v>
+        <v>0.0295</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4967</v>
+        <v>-0.5511</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2802</v>
+        <v>0.1404</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8234</v>
+        <v>1.2635</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.5432</v>
+        <v>-0.8652</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8234</v>
+        <v>1.2635</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9116</v>
+        <v>1.3989</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.5432</v>
+        <v>-0.8652</v>
       </c>
       <c r="K56" t="n">
         <v>102</v>
@@ -3013,7 +3013,7 @@
         <v>44</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3683999999999999</v>
+        <v>0.5337000000000001</v>
       </c>
       <c r="N56" t="n">
         <v>146</v>
@@ -3022,185 +3022,185 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2801</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0588</v>
+        <v>0.0178</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4967</v>
+        <v>-0.576</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2801</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2801</v>
+        <v>0.616</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.4531</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2801</v>
+        <v>0.616</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2947</v>
+        <v>0.6996</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.4531</v>
       </c>
       <c r="K57" t="n">
-        <v>127</v>
+        <v>210</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2947</v>
+        <v>0.2465</v>
       </c>
       <c r="N57" t="n">
-        <v>127</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>krazy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1784</v>
+        <v>0.0823</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0375</v>
+        <v>0.0173</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.543</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1784</v>
+        <v>0.0823</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1784</v>
+        <v>0.4345</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-0.3764</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1784</v>
+        <v>0.4345</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1926</v>
+        <v>0.4811</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-0.3764</v>
       </c>
       <c r="K58" t="n">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1926</v>
+        <v>0.1047</v>
       </c>
       <c r="N58" t="n">
-        <v>152</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1544</v>
+        <v>0.0472</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0324</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.5927</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1544</v>
+        <v>0.0472</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6166</v>
+        <v>0.8238</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.4622</v>
+        <v>-0.5437</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6166</v>
+        <v>0.8238</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7003</v>
+        <v>0.9121</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.4622</v>
+        <v>-0.5437</v>
       </c>
       <c r="K59" t="n">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="L59" t="n">
-        <v>107</v>
+        <v>44</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2381</v>
+        <v>0.3684000000000001</v>
       </c>
       <c r="N59" t="n">
-        <v>317</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1028</v>
+        <v>-0.0041</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0216</v>
+        <v>-0.0009</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5774</v>
+        <v>-0.6157</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1028</v>
+        <v>-0.0041</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5699</v>
+        <v>0.1784</v>
       </c>
       <c r="G60" t="n">
-        <v>0.6727</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5699</v>
+        <v>0.1784</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6309</v>
+        <v>0.1926</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6727</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L60" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.04179999999999995</v>
+        <v>0.1926</v>
       </c>
       <c r="N60" t="n">
-        <v>238</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61">
@@ -3210,31 +3210,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.0429</v>
+        <v>-0.0182</v>
       </c>
       <c r="C61" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.0038</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6047</v>
+        <v>-0.6219</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0429</v>
+        <v>-0.0182</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0521</v>
+        <v>-0.0516</v>
       </c>
       <c r="G61" t="n">
-        <v>0.095</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0521</v>
+        <v>-0.0516</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0577</v>
+        <v>-0.0571</v>
       </c>
       <c r="J61" t="n">
-        <v>0.095</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="K61" t="n">
         <v>97</v>
@@ -3243,7 +3243,7 @@
         <v>63</v>
       </c>
       <c r="M61" t="n">
-        <v>0.0373</v>
+        <v>0.03810000000000001</v>
       </c>
       <c r="N61" t="n">
         <v>160</v>
@@ -3252,93 +3252,93 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>krazy</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0235</v>
+        <v>-0.0288</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0049</v>
+        <v>-0.0061</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6135</v>
+        <v>-0.6267</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0235</v>
+        <v>-0.0288</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4097</v>
+        <v>1.0054</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.3862</v>
+        <v>-1</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4097</v>
+        <v>1.0054</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4536</v>
+        <v>1.1131</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.3862</v>
+        <v>-1</v>
       </c>
       <c r="K62" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
       <c r="L62" t="n">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="M62" t="n">
-        <v>0.06740000000000002</v>
+        <v>0.1131</v>
       </c>
       <c r="N62" t="n">
-        <v>299</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0161</v>
+        <v>-0.0343</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0034</v>
+        <v>-0.0072</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6169</v>
+        <v>-0.6291</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0161</v>
+        <v>-0.0343</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0161</v>
+        <v>-0.5699</v>
       </c>
       <c r="G63" t="n">
-        <v>-1</v>
+        <v>0.6727</v>
       </c>
       <c r="H63" t="n">
-        <v>1.0161</v>
+        <v>-0.5699</v>
       </c>
       <c r="I63" t="n">
-        <v>1.125</v>
+        <v>-0.6309</v>
       </c>
       <c r="J63" t="n">
-        <v>-1</v>
+        <v>0.6727</v>
       </c>
       <c r="K63" t="n">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="L63" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="M63" t="n">
-        <v>0.125</v>
+        <v>0.04179999999999995</v>
       </c>
       <c r="N63" t="n">
-        <v>160</v>
+        <v>238</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.1688</v>
+        <v>-0.1501</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0355</v>
+        <v>-0.0315</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.701</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.1688</v>
+        <v>-0.1501</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.1688</v>
+        <v>-0.1687</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.1688</v>
+        <v>-0.1687</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1869</v>
+        <v>-0.1868</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.1869</v>
+        <v>-0.1868</v>
       </c>
       <c r="N64" t="n">
         <v>213</v>
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2236</v>
+        <v>-0.2029</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.047</v>
+        <v>-0.0426</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.726</v>
+        <v>-0.7045</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2236</v>
+        <v>-0.2029</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2236</v>
+        <v>-0.2255</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2236</v>
+        <v>-0.2255</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2294</v>
+        <v>-0.2313</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2294</v>
+        <v>-0.2313</v>
       </c>
       <c r="N65" t="n">
         <v>88</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3262</v>
+        <v>-0.5308</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1115</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.8509</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3262</v>
+        <v>-0.5308</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.3262</v>
+        <v>-0.3263</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.3262</v>
+        <v>-0.3263</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3262</v>
+        <v>-0.3263</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3262</v>
+        <v>-0.3263</v>
       </c>
       <c r="N66" t="n">
         <v>96</v>
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.5367</v>
+        <v>-0.5783</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1128</v>
+        <v>-0.1215</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8685</v>
+        <v>-0.8721</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5367</v>
+        <v>-0.5783</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.5367</v>
+        <v>-0.5286</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5367</v>
+        <v>-0.5286</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.5647</v>
+        <v>-0.5562</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.5647</v>
+        <v>-0.5562</v>
       </c>
       <c r="N67" t="n">
         <v>127</v>
@@ -3528,415 +3528,415 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5389</v>
+        <v>-0.7081</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1132</v>
+        <v>-0.1488</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.9301</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5389</v>
+        <v>-0.7081</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5389</v>
+        <v>-0.9374</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.3544</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5389</v>
+        <v>-0.9374</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5389</v>
+        <v>-1.0378</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>0.3544</v>
       </c>
       <c r="K68" t="n">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5389</v>
+        <v>-0.6834</v>
       </c>
       <c r="N68" t="n">
-        <v>96</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.5453</v>
+        <v>-0.7346</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1146</v>
+        <v>-0.1543</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8724</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5453</v>
+        <v>-0.7346</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9004</v>
+        <v>-0.6357</v>
       </c>
       <c r="G69" t="n">
-        <v>0.3551</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9004</v>
+        <v>-0.6357</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9969</v>
+        <v>-0.7038</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3551</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>114</v>
+        <v>213</v>
       </c>
       <c r="L69" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6417999999999999</v>
+        <v>-0.7038</v>
       </c>
       <c r="N69" t="n">
-        <v>302</v>
+        <v>213</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6359</v>
+        <v>-0.8146</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1336</v>
+        <v>-0.1711</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9137</v>
+        <v>-0.9777</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6359</v>
+        <v>-0.8146</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6359</v>
+        <v>-0.6216</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6359</v>
+        <v>-0.6216</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.704</v>
+        <v>-0.6541</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.704</v>
+        <v>-0.6541</v>
       </c>
       <c r="N70" t="n">
-        <v>213</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6478</v>
+        <v>-0.8401</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1361</v>
+        <v>-0.1765</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9191</v>
+        <v>-0.9891</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6478</v>
+        <v>-0.8401</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6478</v>
+        <v>-0.5391</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6478</v>
+        <v>-0.5391</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6816</v>
+        <v>-0.5391</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6816</v>
+        <v>-0.5391</v>
       </c>
       <c r="N71" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>nicks</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9316</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.2032</v>
+        <v>-0.1957</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0645</v>
+        <v>-1.0299</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-0.9316</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.1157</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9671999999999999</v>
+        <v>-1.1157</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0177</v>
+        <v>-1.1157</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.0177</v>
+        <v>-1.1157</v>
       </c>
       <c r="N72" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>nicks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0032</v>
+        <v>-1.2272</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.2108</v>
+        <v>-0.2578</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0809</v>
+        <v>-1.162</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0032</v>
+        <v>-1.2272</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0032</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0032</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0291</v>
+        <v>-1.0177</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0291</v>
+        <v>-1.0177</v>
       </c>
       <c r="N73" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0886</v>
+        <v>-1.3495</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.2287</v>
+        <v>-0.2835</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1198</v>
+        <v>-1.2166</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0886</v>
+        <v>-1.3495</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.4492</v>
+        <v>-0.6952</v>
       </c>
       <c r="G74" t="n">
-        <v>0.3606</v>
+        <v>-0.4771</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.4492</v>
+        <v>-0.6952</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.6045</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>0.3606</v>
+        <v>-0.4771</v>
       </c>
       <c r="K74" t="n">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="L74" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.2439</v>
+        <v>-1.2468</v>
       </c>
       <c r="N74" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1157</v>
+        <v>-1.382</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.2344</v>
+        <v>-0.2904</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1321</v>
+        <v>-1.2311</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1157</v>
+        <v>-1.382</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1157</v>
+        <v>-1.4301</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>0.3743</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1157</v>
+        <v>-1.4301</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1157</v>
+        <v>-1.5833</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>0.3743</v>
       </c>
       <c r="K75" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1157</v>
+        <v>-1.209</v>
       </c>
       <c r="N75" t="n">
-        <v>80</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1723</v>
+        <v>-1.4995</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.2463</v>
+        <v>-0.315</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1579</v>
+        <v>-1.2836</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1723</v>
+        <v>-1.4995</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.6952</v>
+        <v>-1.0043</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.4771</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.6952</v>
+        <v>-1.0043</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-1.0302</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.4771</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="L76" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2468</v>
+        <v>-1.0302</v>
       </c>
       <c r="N76" t="n">
-        <v>238</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.2197</v>
+        <v>-1.5445</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.2563</v>
+        <v>-0.3245</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1794</v>
+        <v>-1.3037</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.2197</v>
+        <v>-1.5445</v>
       </c>
       <c r="F77" t="n">
         <v>-1.2197</v>
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.4225</v>
+        <v>-1.6052</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.2989</v>
+        <v>-0.3373</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2718</v>
+        <v>-1.3308</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.4225</v>
+        <v>-1.6052</v>
       </c>
       <c r="F78" t="n">
         <v>-1.4225</v>
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.5725</v>
+        <v>-1.8594</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.3304</v>
+        <v>-0.3907</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.34</v>
+        <v>-1.4444</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.5725</v>
+        <v>-1.8594</v>
       </c>
       <c r="F79" t="n">
         <v>-1.5725</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.594</v>
+        <v>-1.9354</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.3349</v>
+        <v>-0.4066</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3498</v>
+        <v>-1.4783</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.594</v>
+        <v>-1.9354</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.594</v>
+        <v>-1.5783</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.594</v>
+        <v>-1.5783</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.6351</v>
+        <v>-1.619</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.6351</v>
+        <v>-1.619</v>
       </c>
       <c r="N80" t="n">
         <v>88</v>
@@ -4126,93 +4126,93 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Trash</t>
+          <t>aragornN</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-1.768</v>
+        <v>-2.0943</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.3715</v>
+        <v>-0.44</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.429</v>
+        <v>-1.5493</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.768</v>
+        <v>-2.0943</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.768</v>
+        <v>-0.6249</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>-1.2937</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.768</v>
+        <v>-0.6249</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.768</v>
+        <v>-0.6919</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>-1.2937</v>
       </c>
       <c r="K81" t="n">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M81" t="n">
-        <v>-1.768</v>
+        <v>-1.9856</v>
       </c>
       <c r="N81" t="n">
-        <v>80</v>
+        <v>299</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>aragornN</t>
+          <t>Trash</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-1.9181</v>
+        <v>-2.2854</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.403</v>
+        <v>-0.4802</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.4974</v>
+        <v>-1.6347</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.9181</v>
+        <v>-2.2854</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.6246</v>
+        <v>-1.768</v>
       </c>
       <c r="G82" t="n">
-        <v>-1.2935</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.6246</v>
+        <v>-1.768</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.6915</v>
+        <v>-1.768</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.2935</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>168</v>
+        <v>80</v>
       </c>
       <c r="L82" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>-1.985</v>
+        <v>-1.768</v>
       </c>
       <c r="N82" t="n">
-        <v>299</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4312,13 +4312,13 @@
         <v>23</v>
       </c>
       <c r="H2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2563</v>
+        <v>0.2847</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8949</v>
+        <v>6.5481</v>
       </c>
     </row>
     <row r="3">
@@ -4355,10 +4355,10 @@
         <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1445</v>
+        <v>0.1438</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3235</v>
+        <v>3.3074</v>
       </c>
     </row>
     <row r="4">
@@ -4395,10 +4395,10 @@
         <v>0.83</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2152</v>
+        <v>-0.2156</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.9496</v>
+        <v>-4.9588</v>
       </c>
     </row>
     <row r="5">
@@ -4435,10 +4435,10 @@
         <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2453</v>
+        <v>-0.2457</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.6419</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="6">
@@ -4475,10 +4475,10 @@
         <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2453</v>
+        <v>-0.2457</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.6419</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="7">
@@ -5315,10 +5315,10 @@
         <v>1.28</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5598</v>
+        <v>0.5603</v>
       </c>
       <c r="J27" t="n">
-        <v>16.794</v>
+        <v>16.809</v>
       </c>
     </row>
     <row r="28">
@@ -5355,10 +5355,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.167</v>
+        <v>0.1673</v>
       </c>
       <c r="J28" t="n">
-        <v>5.01</v>
+        <v>5.019</v>
       </c>
     </row>
     <row r="29">
@@ -5395,10 +5395,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0716</v>
+        <v>0.0717</v>
       </c>
       <c r="J29" t="n">
-        <v>2.148</v>
+        <v>2.151</v>
       </c>
     </row>
     <row r="30">
@@ -5435,10 +5435,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1255</v>
+        <v>-0.1253</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.765</v>
+        <v>-3.759</v>
       </c>
     </row>
     <row r="31">
@@ -5472,13 +5472,13 @@
         <v>30</v>
       </c>
       <c r="H31" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2242</v>
+        <v>-0.2342</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.726</v>
+        <v>-7.026</v>
       </c>
     </row>
     <row r="32">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7315,10 +7315,10 @@
         <v>1.52</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8012</v>
+        <v>0.8006</v>
       </c>
       <c r="J77" t="n">
-        <v>18.4276</v>
+        <v>18.4138</v>
       </c>
     </row>
     <row r="78">
@@ -7355,10 +7355,10 @@
         <v>1.26</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5094</v>
+        <v>0.509</v>
       </c>
       <c r="J78" t="n">
-        <v>11.7162</v>
+        <v>11.707</v>
       </c>
     </row>
     <row r="79">
@@ -7395,10 +7395,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2421</v>
+        <v>-0.2423</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.5683</v>
+        <v>-5.5729</v>
       </c>
     </row>
     <row r="80">
@@ -7432,13 +7432,13 @@
         <v>23</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2521</v>
+        <v>-0.2423</v>
       </c>
       <c r="J80" t="n">
-        <v>-5.7983</v>
+        <v>-5.5729</v>
       </c>
     </row>
     <row r="81">
@@ -7475,10 +7475,10 @@
         <v>0.59</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4456</v>
+        <v>-0.4458</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.2488</v>
+        <v>-10.2534</v>
       </c>
     </row>
     <row r="82">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -7715,10 +7715,10 @@
         <v>1.14</v>
       </c>
       <c r="I87" t="n">
-        <v>0.2681</v>
+        <v>0.2677</v>
       </c>
       <c r="J87" t="n">
-        <v>5.8982</v>
+        <v>5.8894</v>
       </c>
     </row>
     <row r="88">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7755,10 +7755,10 @@
         <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.0061</v>
+        <v>0.0058</v>
       </c>
       <c r="J88" t="n">
-        <v>0.1342</v>
+        <v>0.1276</v>
       </c>
     </row>
     <row r="89">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7795,10 +7795,10 @@
         <v>0.93</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.107</v>
+        <v>-0.1071</v>
       </c>
       <c r="J89" t="n">
-        <v>-2.354</v>
+        <v>-2.3562</v>
       </c>
     </row>
     <row r="90">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7835,10 +7835,10 @@
         <v>0.92</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1188</v>
+        <v>-0.119</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.6136</v>
+        <v>-2.618</v>
       </c>
     </row>
     <row r="91">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7872,13 +7872,13 @@
         <v>22</v>
       </c>
       <c r="H91" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.342</v>
+        <v>-0.3329</v>
       </c>
       <c r="J91" t="n">
-        <v>-7.524</v>
+        <v>-7.3238</v>
       </c>
     </row>
     <row r="92">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -7915,10 +7915,10 @@
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0439</v>
+        <v>0.0445</v>
       </c>
       <c r="J92" t="n">
-        <v>0.878</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="93">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -7955,10 +7955,10 @@
         <v>0.93</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0914</v>
+        <v>-0.0911</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.828</v>
+        <v>-1.822</v>
       </c>
     </row>
     <row r="94">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -7995,10 +7995,10 @@
         <v>0.75</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2804</v>
+        <v>-0.2802</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.608</v>
+        <v>-5.604</v>
       </c>
     </row>
     <row r="95">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -8032,13 +8032,13 @@
         <v>20</v>
       </c>
       <c r="H95" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3722</v>
+        <v>-0.381</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.444</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="96">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -8075,10 +8075,10 @@
         <v>0.63</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3902</v>
+        <v>-0.39</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.804</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="97">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8715,10 +8715,10 @@
         <v>0.92</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0978</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.4565</v>
+        <v>-1.467</v>
       </c>
     </row>
     <row r="113">
@@ -8755,16 +8755,16 @@
         <v>0.87</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1563</v>
+        <v>-0.1569</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.3445</v>
+        <v>-2.3535</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8792,13 +8792,13 @@
         <v>15</v>
       </c>
       <c r="H114" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.286</v>
+        <v>-0.2684</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.29</v>
+        <v>-4.026</v>
       </c>
     </row>
     <row r="115">
@@ -8835,10 +8835,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3765</v>
+        <v>-0.377</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.6475</v>
+        <v>-5.655</v>
       </c>
     </row>
     <row r="116">
@@ -8875,10 +8875,10 @@
         <v>0.59</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4212</v>
+        <v>-0.4217</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.318</v>
+        <v>-6.3255</v>
       </c>
     </row>
     <row r="117">
@@ -9124,7 +9124,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11115,10 +11115,10 @@
         <v>1.61</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0862</v>
+        <v>1.0858</v>
       </c>
       <c r="J172" t="n">
-        <v>21.724</v>
+        <v>21.716</v>
       </c>
     </row>
     <row r="173">
@@ -11155,10 +11155,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>0.9806</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J173" t="n">
-        <v>19.612</v>
+        <v>19.606</v>
       </c>
     </row>
     <row r="174">
@@ -11192,13 +11192,13 @@
         <v>20</v>
       </c>
       <c r="H174" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8034</v>
+        <v>0.8171</v>
       </c>
       <c r="J174" t="n">
-        <v>16.068</v>
+        <v>16.342</v>
       </c>
     </row>
     <row r="175">
@@ -11235,10 +11235,10 @@
         <v>1.37</v>
       </c>
       <c r="I175" t="n">
-        <v>0.7614</v>
+        <v>0.7611</v>
       </c>
       <c r="J175" t="n">
-        <v>15.228</v>
+        <v>15.222</v>
       </c>
     </row>
     <row r="176">
@@ -11275,10 +11275,10 @@
         <v>0.52</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.2171</v>
+        <v>-1.2173</v>
       </c>
       <c r="J176" t="n">
-        <v>-24.342</v>
+        <v>-24.346</v>
       </c>
     </row>
     <row r="177">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11969,7 +11969,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12369,7 +12369,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -13715,10 +13715,10 @@
         <v>1.3</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7684</v>
+        <v>0.7679</v>
       </c>
       <c r="J237" t="n">
-        <v>31.5044</v>
+        <v>31.4839</v>
       </c>
     </row>
     <row r="238">
@@ -13755,10 +13755,10 @@
         <v>1.21</v>
       </c>
       <c r="I238" t="n">
-        <v>0.577</v>
+        <v>0.5766</v>
       </c>
       <c r="J238" t="n">
-        <v>23.657</v>
+        <v>23.6406</v>
       </c>
     </row>
     <row r="239">
@@ -13792,13 +13792,13 @@
         <v>41</v>
       </c>
       <c r="H239" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2402</v>
+        <v>0.2677</v>
       </c>
       <c r="J239" t="n">
-        <v>9.8482</v>
+        <v>10.9757</v>
       </c>
     </row>
     <row r="240">
@@ -13835,10 +13835,10 @@
         <v>1.05</v>
       </c>
       <c r="I240" t="n">
-        <v>0.1814</v>
+        <v>0.1811</v>
       </c>
       <c r="J240" t="n">
-        <v>7.4374</v>
+        <v>7.4251</v>
       </c>
     </row>
     <row r="241">
@@ -13875,10 +13875,10 @@
         <v>1.02</v>
       </c>
       <c r="I241" t="n">
-        <v>0.08</v>
+        <v>0.0796</v>
       </c>
       <c r="J241" t="n">
-        <v>3.28</v>
+        <v>3.2636</v>
       </c>
     </row>
     <row r="242">
@@ -15115,10 +15115,10 @@
         <v>1.18</v>
       </c>
       <c r="I272" t="n">
-        <v>0.525</v>
+        <v>0.5245</v>
       </c>
       <c r="J272" t="n">
-        <v>18.9</v>
+        <v>18.882</v>
       </c>
     </row>
     <row r="273">
@@ -15152,13 +15152,13 @@
         <v>36</v>
       </c>
       <c r="H273" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3298</v>
+        <v>0.3552</v>
       </c>
       <c r="J273" t="n">
-        <v>11.8728</v>
+        <v>12.7872</v>
       </c>
     </row>
     <row r="274">
@@ -15195,10 +15195,10 @@
         <v>1.1</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3298</v>
+        <v>0.3295</v>
       </c>
       <c r="J274" t="n">
-        <v>11.8728</v>
+        <v>11.862</v>
       </c>
     </row>
     <row r="275">
@@ -15235,10 +15235,10 @@
         <v>1.08</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2768</v>
+        <v>0.2765</v>
       </c>
       <c r="J275" t="n">
-        <v>9.9648</v>
+        <v>9.954000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -15275,10 +15275,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.529</v>
+        <v>-0.5294</v>
       </c>
       <c r="J276" t="n">
-        <v>-19.044</v>
+        <v>-19.0584</v>
       </c>
     </row>
     <row r="277">
@@ -15715,10 +15715,10 @@
         <v>1.42</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5544</v>
+        <v>0.554</v>
       </c>
       <c r="J287" t="n">
-        <v>16.0776</v>
+        <v>16.066</v>
       </c>
     </row>
     <row r="288">
@@ -15755,10 +15755,10 @@
         <v>1.22</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3292</v>
+        <v>0.329</v>
       </c>
       <c r="J288" t="n">
-        <v>9.546799999999999</v>
+        <v>9.541</v>
       </c>
     </row>
     <row r="289">
@@ -15792,13 +15792,13 @@
         <v>29</v>
       </c>
       <c r="H289" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2554</v>
+        <v>0.2678</v>
       </c>
       <c r="J289" t="n">
-        <v>7.4066</v>
+        <v>7.7662</v>
       </c>
     </row>
     <row r="290">
@@ -15835,10 +15835,10 @@
         <v>0.95</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.096</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.784</v>
+        <v>-2.7898</v>
       </c>
     </row>
     <row r="291">
@@ -15875,10 +15875,10 @@
         <v>0.87</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1908</v>
+        <v>-0.1909</v>
       </c>
       <c r="J291" t="n">
-        <v>-5.5332</v>
+        <v>-5.5361</v>
       </c>
     </row>
     <row r="292">
@@ -16712,13 +16712,13 @@
         <v>22</v>
       </c>
       <c r="H312" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="I312" t="n">
-        <v>1.4843</v>
+        <v>1.4237</v>
       </c>
       <c r="J312" t="n">
-        <v>32.6546</v>
+        <v>31.3214</v>
       </c>
     </row>
     <row r="313">
@@ -16755,10 +16755,10 @@
         <v>1.27</v>
       </c>
       <c r="I313" t="n">
-        <v>0.6901</v>
+        <v>0.6921</v>
       </c>
       <c r="J313" t="n">
-        <v>15.1822</v>
+        <v>15.2262</v>
       </c>
     </row>
     <row r="314">
@@ -16792,13 +16792,13 @@
         <v>22</v>
       </c>
       <c r="H314" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="I314" t="n">
-        <v>0.6073</v>
+        <v>0.5665</v>
       </c>
       <c r="J314" t="n">
-        <v>13.3606</v>
+        <v>12.463</v>
       </c>
     </row>
     <row r="315">
@@ -16835,10 +16835,10 @@
         <v>1.18</v>
       </c>
       <c r="I315" t="n">
-        <v>0.5008</v>
+        <v>0.5022</v>
       </c>
       <c r="J315" t="n">
-        <v>11.0176</v>
+        <v>11.0484</v>
       </c>
     </row>
     <row r="316">
@@ -16872,13 +16872,13 @@
         <v>22</v>
       </c>
       <c r="H316" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I316" t="n">
-        <v>-1.0911</v>
+        <v>-1.0697</v>
       </c>
       <c r="J316" t="n">
-        <v>-24.0042</v>
+        <v>-23.5334</v>
       </c>
     </row>
     <row r="317">
@@ -16912,13 +16912,13 @@
         <v>22</v>
       </c>
       <c r="H317" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="I317" t="n">
-        <v>1.0579</v>
+        <v>1.0456</v>
       </c>
       <c r="J317" t="n">
-        <v>23.2738</v>
+        <v>23.0032</v>
       </c>
     </row>
     <row r="318">
@@ -16955,10 +16955,10 @@
         <v>1.24</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5059</v>
+        <v>0.5049</v>
       </c>
       <c r="J318" t="n">
-        <v>11.1298</v>
+        <v>11.1078</v>
       </c>
     </row>
     <row r="319">
@@ -16992,13 +16992,13 @@
         <v>22</v>
       </c>
       <c r="H319" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.2991</v>
+        <v>-0.2899</v>
       </c>
       <c r="J319" t="n">
-        <v>-6.5802</v>
+        <v>-6.3778</v>
       </c>
     </row>
     <row r="320">
@@ -17032,13 +17032,13 @@
         <v>22</v>
       </c>
       <c r="H320" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3551</v>
+        <v>-0.3462</v>
       </c>
       <c r="J320" t="n">
-        <v>-7.8122</v>
+        <v>-7.6164</v>
       </c>
     </row>
     <row r="321">
@@ -17072,13 +17072,13 @@
         <v>22</v>
       </c>
       <c r="H321" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4356</v>
+        <v>-0.4271</v>
       </c>
       <c r="J321" t="n">
-        <v>-9.5832</v>
+        <v>-9.3962</v>
       </c>
     </row>
     <row r="322">
@@ -17115,10 +17115,10 @@
         <v>1.34</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5306</v>
+        <v>0.5301</v>
       </c>
       <c r="J322" t="n">
-        <v>11.1426</v>
+        <v>11.1321</v>
       </c>
     </row>
     <row r="323">
@@ -17155,10 +17155,10 @@
         <v>0.95</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.0827</v>
+        <v>-0.0828</v>
       </c>
       <c r="J323" t="n">
-        <v>-1.7367</v>
+        <v>-1.7388</v>
       </c>
     </row>
     <row r="324">
@@ -17195,10 +17195,10 @@
         <v>0.91</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.131</v>
+        <v>-0.1312</v>
       </c>
       <c r="J324" t="n">
-        <v>-2.751</v>
+        <v>-2.7552</v>
       </c>
     </row>
     <row r="325">
@@ -17235,10 +17235,10 @@
         <v>0.9</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1424</v>
+        <v>-0.1426</v>
       </c>
       <c r="J325" t="n">
-        <v>-2.9904</v>
+        <v>-2.9946</v>
       </c>
     </row>
     <row r="326">
@@ -17272,13 +17272,13 @@
         <v>21</v>
       </c>
       <c r="H326" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4061</v>
+        <v>-0.3974</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.5281</v>
+        <v>-8.3454</v>
       </c>
     </row>
     <row r="327">
@@ -17315,10 +17315,10 @@
         <v>1.87</v>
       </c>
       <c r="I327" t="n">
-        <v>0.9614</v>
+        <v>0.9621</v>
       </c>
       <c r="J327" t="n">
-        <v>20.1894</v>
+        <v>20.2041</v>
       </c>
     </row>
     <row r="328">
@@ -17355,10 +17355,10 @@
         <v>1.29</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3951</v>
+        <v>0.3952</v>
       </c>
       <c r="J328" t="n">
-        <v>8.2971</v>
+        <v>8.299200000000001</v>
       </c>
     </row>
     <row r="329">
@@ -17395,10 +17395,10 @@
         <v>1.22</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3165</v>
+        <v>0.3168</v>
       </c>
       <c r="J329" t="n">
-        <v>6.6465</v>
+        <v>6.6528</v>
       </c>
     </row>
     <row r="330">
@@ -17432,13 +17432,13 @@
         <v>21</v>
       </c>
       <c r="H330" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="I330" t="n">
-        <v>0.23</v>
+        <v>0.2172</v>
       </c>
       <c r="J330" t="n">
-        <v>4.83</v>
+        <v>4.5612</v>
       </c>
     </row>
     <row r="331">
@@ -17472,13 +17472,13 @@
         <v>21</v>
       </c>
       <c r="H331" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.1219</v>
+        <v>-0.1342</v>
       </c>
       <c r="J331" t="n">
-        <v>-2.5599</v>
+        <v>-2.8182</v>
       </c>
     </row>
     <row r="332">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -17929,7 +17929,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D347" t="n">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D348" t="n">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D349" t="n">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -18315,10 +18315,10 @@
         <v>1.24</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6409</v>
+        <v>0.6413</v>
       </c>
       <c r="J352" t="n">
-        <v>14.7407</v>
+        <v>14.7499</v>
       </c>
     </row>
     <row r="353">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -18352,13 +18352,13 @@
         <v>23</v>
       </c>
       <c r="H353" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I353" t="n">
-        <v>0.5092</v>
+        <v>0.4869</v>
       </c>
       <c r="J353" t="n">
-        <v>11.7116</v>
+        <v>11.1987</v>
       </c>
     </row>
     <row r="354">
@@ -18369,7 +18369,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -18395,10 +18395,10 @@
         <v>1.17</v>
       </c>
       <c r="I354" t="n">
-        <v>0.4866</v>
+        <v>0.4869</v>
       </c>
       <c r="J354" t="n">
-        <v>11.1918</v>
+        <v>11.1987</v>
       </c>
     </row>
     <row r="355">
@@ -18409,7 +18409,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -18435,10 +18435,10 @@
         <v>1.08</v>
       </c>
       <c r="I355" t="n">
-        <v>0.2671</v>
+        <v>0.2674</v>
       </c>
       <c r="J355" t="n">
-        <v>6.1433</v>
+        <v>6.1502</v>
       </c>
     </row>
     <row r="356">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -18475,10 +18475,10 @@
         <v>1.01</v>
       </c>
       <c r="I356" t="n">
-        <v>0.0376</v>
+        <v>0.0379</v>
       </c>
       <c r="J356" t="n">
-        <v>0.8648</v>
+        <v>0.8717</v>
       </c>
     </row>
     <row r="357">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -18654,7 +18654,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -18715,10 +18715,10 @@
         <v>1.78</v>
       </c>
       <c r="I362" t="n">
-        <v>1.4899</v>
+        <v>1.4892</v>
       </c>
       <c r="J362" t="n">
-        <v>34.2677</v>
+        <v>34.2516</v>
       </c>
     </row>
     <row r="363">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -18755,10 +18755,10 @@
         <v>1.14</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4163</v>
+        <v>0.4161</v>
       </c>
       <c r="J363" t="n">
-        <v>9.5749</v>
+        <v>9.5703</v>
       </c>
     </row>
     <row r="364">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -18792,13 +18792,13 @@
         <v>23</v>
       </c>
       <c r="H364" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I364" t="n">
-        <v>0.2645</v>
+        <v>0.2912</v>
       </c>
       <c r="J364" t="n">
-        <v>6.0835</v>
+        <v>6.6976</v>
       </c>
     </row>
     <row r="365">
@@ -18809,7 +18809,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -18835,10 +18835,10 @@
         <v>0.92</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3169</v>
+        <v>-0.3173</v>
       </c>
       <c r="J365" t="n">
-        <v>-7.2887</v>
+        <v>-7.2979</v>
       </c>
     </row>
     <row r="366">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -18875,10 +18875,10 @@
         <v>0.84</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.523</v>
+        <v>-0.5234</v>
       </c>
       <c r="J366" t="n">
-        <v>-12.029</v>
+        <v>-12.0382</v>
       </c>
     </row>
     <row r="367">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -19884,7 +19884,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -20684,7 +20684,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -20715,10 +20715,10 @@
         <v>1.76</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4164</v>
+        <v>1.4168</v>
       </c>
       <c r="J412" t="n">
-        <v>25.4952</v>
+        <v>25.5024</v>
       </c>
     </row>
     <row r="413">
@@ -20755,10 +20755,10 @@
         <v>1.72</v>
       </c>
       <c r="I413" t="n">
-        <v>1.3662</v>
+        <v>1.3666</v>
       </c>
       <c r="J413" t="n">
-        <v>24.5916</v>
+        <v>24.5988</v>
       </c>
     </row>
     <row r="414">
@@ -20795,10 +20795,10 @@
         <v>1.17</v>
       </c>
       <c r="I414" t="n">
-        <v>0.461</v>
+        <v>0.4613</v>
       </c>
       <c r="J414" t="n">
-        <v>8.298</v>
+        <v>8.3034</v>
       </c>
     </row>
     <row r="415">
@@ -20835,10 +20835,10 @@
         <v>1.05</v>
       </c>
       <c r="I415" t="n">
-        <v>0.1485</v>
+        <v>0.1488</v>
       </c>
       <c r="J415" t="n">
-        <v>2.673</v>
+        <v>2.6784</v>
       </c>
     </row>
     <row r="416">
@@ -20872,13 +20872,13 @@
         <v>18</v>
       </c>
       <c r="H416" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.318</v>
+        <v>-0.346</v>
       </c>
       <c r="J416" t="n">
-        <v>-5.724</v>
+        <v>-6.228</v>
       </c>
     </row>
     <row r="417">
@@ -22712,13 +22712,13 @@
         <v>15</v>
       </c>
       <c r="H462" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I462" t="n">
-        <v>-0.1574</v>
+        <v>-0.1359</v>
       </c>
       <c r="J462" t="n">
-        <v>-2.361</v>
+        <v>-2.0385</v>
       </c>
     </row>
     <row r="463">
@@ -22755,10 +22755,10 @@
         <v>0.75</v>
       </c>
       <c r="I463" t="n">
-        <v>-0.2549</v>
+        <v>-0.2563</v>
       </c>
       <c r="J463" t="n">
-        <v>-3.8235</v>
+        <v>-3.8445</v>
       </c>
     </row>
     <row r="464">
@@ -22795,10 +22795,10 @@
         <v>0.58</v>
       </c>
       <c r="I464" t="n">
-        <v>-0.4115</v>
+        <v>-0.4122</v>
       </c>
       <c r="J464" t="n">
-        <v>-6.1725</v>
+        <v>-6.183</v>
       </c>
     </row>
     <row r="465">
@@ -22832,13 +22832,13 @@
         <v>15</v>
       </c>
       <c r="H465" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I465" t="n">
-        <v>-0.4637</v>
+        <v>-0.4558</v>
       </c>
       <c r="J465" t="n">
-        <v>-6.9555</v>
+        <v>-6.837</v>
       </c>
     </row>
     <row r="466">
@@ -22875,10 +22875,10 @@
         <v>0.35</v>
       </c>
       <c r="I466" t="n">
-        <v>-0.6135</v>
+        <v>-0.6143</v>
       </c>
       <c r="J466" t="n">
-        <v>-9.202500000000001</v>
+        <v>-9.214499999999999</v>
       </c>
     </row>
     <row r="467">
@@ -22912,13 +22912,13 @@
         <v>15</v>
       </c>
       <c r="H467" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="I467" t="n">
-        <v>1.8421</v>
+        <v>1.8361</v>
       </c>
       <c r="J467" t="n">
-        <v>27.6315</v>
+        <v>27.5415</v>
       </c>
     </row>
     <row r="468">
@@ -22952,13 +22952,13 @@
         <v>15</v>
       </c>
       <c r="H468" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I468" t="n">
-        <v>1.2523</v>
+        <v>1.2426</v>
       </c>
       <c r="J468" t="n">
-        <v>18.7845</v>
+        <v>18.639</v>
       </c>
     </row>
     <row r="469">
@@ -22992,13 +22992,13 @@
         <v>15</v>
       </c>
       <c r="H469" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="I469" t="n">
-        <v>1.2163</v>
+        <v>1.1335</v>
       </c>
       <c r="J469" t="n">
-        <v>18.2445</v>
+        <v>17.0025</v>
       </c>
     </row>
     <row r="470">
@@ -23032,13 +23032,13 @@
         <v>15</v>
       </c>
       <c r="H470" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I470" t="n">
-        <v>1.1318</v>
+        <v>1.0962</v>
       </c>
       <c r="J470" t="n">
-        <v>16.977</v>
+        <v>16.443</v>
       </c>
     </row>
     <row r="471">
@@ -23072,13 +23072,13 @@
         <v>15</v>
       </c>
       <c r="H471" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I471" t="n">
-        <v>-0.23</v>
+        <v>-0.2605</v>
       </c>
       <c r="J471" t="n">
-        <v>-3.45</v>
+        <v>-3.9075</v>
       </c>
     </row>
     <row r="472">
@@ -23512,13 +23512,13 @@
         <v>20</v>
       </c>
       <c r="H482" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="I482" t="n">
-        <v>1.1865</v>
+        <v>1.1737</v>
       </c>
       <c r="J482" t="n">
-        <v>23.73</v>
+        <v>23.474</v>
       </c>
     </row>
     <row r="483">
@@ -23555,10 +23555,10 @@
         <v>1.56</v>
       </c>
       <c r="I483" t="n">
-        <v>1.1732</v>
+        <v>1.1737</v>
       </c>
       <c r="J483" t="n">
-        <v>23.464</v>
+        <v>23.474</v>
       </c>
     </row>
     <row r="484">
@@ -23595,10 +23595,10 @@
         <v>1.34</v>
       </c>
       <c r="I484" t="n">
-        <v>0.8219</v>
+        <v>0.8222</v>
       </c>
       <c r="J484" t="n">
-        <v>16.438</v>
+        <v>16.444</v>
       </c>
     </row>
     <row r="485">
@@ -23635,10 +23635,10 @@
         <v>0.98</v>
       </c>
       <c r="I485" t="n">
-        <v>-0.1449</v>
+        <v>-0.1445</v>
       </c>
       <c r="J485" t="n">
-        <v>-2.898</v>
+        <v>-2.89</v>
       </c>
     </row>
     <row r="486">
@@ -23675,10 +23675,10 @@
         <v>0.84</v>
       </c>
       <c r="I486" t="n">
-        <v>-0.5411</v>
+        <v>-0.5407</v>
       </c>
       <c r="J486" t="n">
-        <v>-10.822</v>
+        <v>-10.814</v>
       </c>
     </row>
     <row r="487">
@@ -24715,10 +24715,10 @@
         <v>1.72</v>
       </c>
       <c r="I512" t="n">
-        <v>0.834</v>
+        <v>0.8337</v>
       </c>
       <c r="J512" t="n">
-        <v>16.68</v>
+        <v>16.674</v>
       </c>
     </row>
     <row r="513">
@@ -24755,10 +24755,10 @@
         <v>1.4</v>
       </c>
       <c r="I513" t="n">
-        <v>0.516</v>
+        <v>0.5158</v>
       </c>
       <c r="J513" t="n">
-        <v>10.32</v>
+        <v>10.316</v>
       </c>
     </row>
     <row r="514">
@@ -24795,10 +24795,10 @@
         <v>1.29</v>
       </c>
       <c r="I514" t="n">
-        <v>0.3981</v>
+        <v>0.398</v>
       </c>
       <c r="J514" t="n">
-        <v>7.962</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="515">
@@ -24832,13 +24832,13 @@
         <v>20</v>
       </c>
       <c r="H515" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I515" t="n">
-        <v>-0.0175</v>
+        <v>0.0102</v>
       </c>
       <c r="J515" t="n">
-        <v>-0.35</v>
+        <v>0.204</v>
       </c>
     </row>
     <row r="516">
@@ -24875,10 +24875,10 @@
         <v>0.8</v>
       </c>
       <c r="I516" t="n">
-        <v>-0.2717</v>
+        <v>-0.2718</v>
       </c>
       <c r="J516" t="n">
-        <v>-5.434</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="517">
@@ -25115,10 +25115,10 @@
         <v>1.14</v>
       </c>
       <c r="I522" t="n">
-        <v>0.3683</v>
+        <v>0.3676</v>
       </c>
       <c r="J522" t="n">
-        <v>6.6294</v>
+        <v>6.6168</v>
       </c>
     </row>
     <row r="523">
@@ -25155,10 +25155,10 @@
         <v>1.11</v>
       </c>
       <c r="I523" t="n">
-        <v>0.3096</v>
+        <v>0.3089</v>
       </c>
       <c r="J523" t="n">
-        <v>5.5728</v>
+        <v>5.5602</v>
       </c>
     </row>
     <row r="524">
@@ -25195,10 +25195,10 @@
         <v>0.79</v>
       </c>
       <c r="I524" t="n">
-        <v>-0.2481</v>
+        <v>-0.2483</v>
       </c>
       <c r="J524" t="n">
-        <v>-4.4658</v>
+        <v>-4.4694</v>
       </c>
     </row>
     <row r="525">
@@ -25232,13 +25232,13 @@
         <v>18</v>
       </c>
       <c r="H525" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I525" t="n">
-        <v>-0.4147</v>
+        <v>-0.406</v>
       </c>
       <c r="J525" t="n">
-        <v>-7.4646</v>
+        <v>-7.308</v>
       </c>
     </row>
     <row r="526">
@@ -25275,10 +25275,10 @@
         <v>0.61</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.4147</v>
+        <v>-0.4149</v>
       </c>
       <c r="J526" t="n">
-        <v>-7.4646</v>
+        <v>-7.4682</v>
       </c>
     </row>
     <row r="527">
@@ -25315,10 +25315,10 @@
         <v>1.95</v>
       </c>
       <c r="I527" t="n">
-        <v>1.6422</v>
+        <v>1.6427</v>
       </c>
       <c r="J527" t="n">
-        <v>29.5596</v>
+        <v>29.5686</v>
       </c>
     </row>
     <row r="528">
@@ -25355,10 +25355,10 @@
         <v>1.57</v>
       </c>
       <c r="I528" t="n">
-        <v>1.1691</v>
+        <v>1.1695</v>
       </c>
       <c r="J528" t="n">
-        <v>21.0438</v>
+        <v>21.051</v>
       </c>
     </row>
     <row r="529">
@@ -25395,10 +25395,10 @@
         <v>1.18</v>
       </c>
       <c r="I529" t="n">
-        <v>0.4796</v>
+        <v>0.4799</v>
       </c>
       <c r="J529" t="n">
-        <v>8.6328</v>
+        <v>8.638199999999999</v>
       </c>
     </row>
     <row r="530">
@@ -25435,10 +25435,10 @@
         <v>1.07</v>
       </c>
       <c r="I530" t="n">
-        <v>0.2034</v>
+        <v>0.2037</v>
       </c>
       <c r="J530" t="n">
-        <v>3.6612</v>
+        <v>3.6666</v>
       </c>
     </row>
     <row r="531">
@@ -25472,13 +25472,13 @@
         <v>18</v>
       </c>
       <c r="H531" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I531" t="n">
-        <v>-0.0591</v>
+        <v>-0.1186</v>
       </c>
       <c r="J531" t="n">
-        <v>-1.0638</v>
+        <v>-2.1348</v>
       </c>
     </row>
     <row r="532">
@@ -25515,10 +25515,10 @@
         <v>1.19</v>
       </c>
       <c r="I532" t="n">
-        <v>0.4084</v>
+        <v>0.4081</v>
       </c>
       <c r="J532" t="n">
-        <v>8.9848</v>
+        <v>8.978199999999999</v>
       </c>
     </row>
     <row r="533">
@@ -25552,13 +25552,13 @@
         <v>22</v>
       </c>
       <c r="H533" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="I533" t="n">
-        <v>0.3388</v>
+        <v>0.3562</v>
       </c>
       <c r="J533" t="n">
-        <v>7.4536</v>
+        <v>7.8364</v>
       </c>
     </row>
     <row r="534">
@@ -25595,10 +25595,10 @@
         <v>1.03</v>
       </c>
       <c r="I534" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="J534" t="n">
-        <v>2.1252</v>
+        <v>2.1208</v>
       </c>
     </row>
     <row r="535">
@@ -25635,10 +25635,10 @@
         <v>0.95</v>
       </c>
       <c r="I535" t="n">
-        <v>-0.0891</v>
+        <v>-0.0892</v>
       </c>
       <c r="J535" t="n">
-        <v>-1.9602</v>
+        <v>-1.9624</v>
       </c>
     </row>
     <row r="536">
@@ -25675,10 +25675,10 @@
         <v>0.87</v>
       </c>
       <c r="I536" t="n">
-        <v>-0.1835</v>
+        <v>-0.1837</v>
       </c>
       <c r="J536" t="n">
-        <v>-4.037</v>
+        <v>-4.0414</v>
       </c>
     </row>
     <row r="537">
@@ -26294,7 +26294,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D552" t="n">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D553" t="n">
@@ -26374,7 +26374,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -26512,13 +26512,13 @@
         <v>30</v>
       </c>
       <c r="H557" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I557" t="n">
-        <v>0.6022</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J557" t="n">
-        <v>18.066</v>
+        <v>18.372</v>
       </c>
     </row>
     <row r="558">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -26555,10 +26555,10 @@
         <v>1.3</v>
       </c>
       <c r="I558" t="n">
-        <v>0.4265</v>
+        <v>0.4262</v>
       </c>
       <c r="J558" t="n">
-        <v>12.795</v>
+        <v>12.786</v>
       </c>
     </row>
     <row r="559">
@@ -26569,7 +26569,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -26595,10 +26595,10 @@
         <v>0.96</v>
       </c>
       <c r="I559" t="n">
-        <v>-0.0801</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J559" t="n">
-        <v>-2.403</v>
+        <v>-2.406</v>
       </c>
     </row>
     <row r="560">
@@ -26609,7 +26609,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -26635,10 +26635,10 @@
         <v>0.89</v>
       </c>
       <c r="I560" t="n">
-        <v>-0.1664</v>
+        <v>-0.1666</v>
       </c>
       <c r="J560" t="n">
-        <v>-4.992</v>
+        <v>-4.998</v>
       </c>
     </row>
     <row r="561">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -26675,10 +26675,10 @@
         <v>0.87</v>
       </c>
       <c r="I561" t="n">
-        <v>-0.1885</v>
+        <v>-0.1886</v>
       </c>
       <c r="J561" t="n">
-        <v>-5.655</v>
+        <v>-5.658</v>
       </c>
     </row>
     <row r="562">
@@ -26694,7 +26694,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D562" t="n">
@@ -26734,7 +26734,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D563" t="n">
@@ -26774,7 +26774,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D564" t="n">
@@ -26814,7 +26814,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D566" t="n">
@@ -26889,7 +26889,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -26915,10 +26915,10 @@
         <v>1.23</v>
       </c>
       <c r="I567" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.509</v>
       </c>
       <c r="J567" t="n">
-        <v>10.7016</v>
+        <v>10.689</v>
       </c>
     </row>
     <row r="568">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -26955,10 +26955,10 @@
         <v>0.95</v>
       </c>
       <c r="I568" t="n">
-        <v>-0.0803</v>
+        <v>-0.0805</v>
       </c>
       <c r="J568" t="n">
-        <v>-1.6863</v>
+        <v>-1.6905</v>
       </c>
     </row>
     <row r="569">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -26995,10 +26995,10 @@
         <v>0.88</v>
       </c>
       <c r="I569" t="n">
-        <v>-0.1618</v>
+        <v>-0.162</v>
       </c>
       <c r="J569" t="n">
-        <v>-3.3978</v>
+        <v>-3.402</v>
       </c>
     </row>
     <row r="570">
@@ -27009,7 +27009,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -27035,10 +27035,10 @@
         <v>0.87</v>
       </c>
       <c r="I570" t="n">
-        <v>-0.1725</v>
+        <v>-0.1727</v>
       </c>
       <c r="J570" t="n">
-        <v>-3.6225</v>
+        <v>-3.6267</v>
       </c>
     </row>
     <row r="571">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -27072,13 +27072,13 @@
         <v>21</v>
       </c>
       <c r="H571" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.4029</v>
+        <v>-0.3941</v>
       </c>
       <c r="J571" t="n">
-        <v>-8.460900000000001</v>
+        <v>-8.2761</v>
       </c>
     </row>
     <row r="572">
@@ -27094,7 +27094,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D572" t="n">
@@ -27134,7 +27134,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D573" t="n">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D574" t="n">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -27254,7 +27254,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D576" t="n">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -27329,7 +27329,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -27409,7 +27409,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -29312,13 +29312,13 @@
         <v>17</v>
       </c>
       <c r="H627" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="I627" t="n">
-        <v>0.7109</v>
+        <v>0.7202</v>
       </c>
       <c r="J627" t="n">
-        <v>12.0853</v>
+        <v>12.2434</v>
       </c>
     </row>
     <row r="628">
@@ -29355,10 +29355,10 @@
         <v>1.43</v>
       </c>
       <c r="I628" t="n">
-        <v>0.5352</v>
+        <v>0.535</v>
       </c>
       <c r="J628" t="n">
-        <v>9.0984</v>
+        <v>9.095000000000001</v>
       </c>
     </row>
     <row r="629">
@@ -29395,10 +29395,10 @@
         <v>1.35</v>
       </c>
       <c r="I629" t="n">
-        <v>0.4547</v>
+        <v>0.4546</v>
       </c>
       <c r="J629" t="n">
-        <v>7.7299</v>
+        <v>7.7282</v>
       </c>
     </row>
     <row r="630">
@@ -29435,10 +29435,10 @@
         <v>1.25</v>
       </c>
       <c r="I630" t="n">
-        <v>0.3462</v>
+        <v>0.346</v>
       </c>
       <c r="J630" t="n">
-        <v>5.8854</v>
+        <v>5.882</v>
       </c>
     </row>
     <row r="631">
@@ -29475,10 +29475,10 @@
         <v>1.16</v>
       </c>
       <c r="I631" t="n">
-        <v>0.2373</v>
+        <v>0.2371</v>
       </c>
       <c r="J631" t="n">
-        <v>4.0341</v>
+        <v>4.0307</v>
       </c>
     </row>
     <row r="632">
@@ -29512,13 +29512,13 @@
         <v>21</v>
       </c>
       <c r="H632" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I632" t="n">
-        <v>1.4465</v>
+        <v>1.4343</v>
       </c>
       <c r="J632" t="n">
-        <v>30.3765</v>
+        <v>30.1203</v>
       </c>
     </row>
     <row r="633">
@@ -29555,10 +29555,10 @@
         <v>1.5</v>
       </c>
       <c r="I633" t="n">
-        <v>1.0934</v>
+        <v>1.0938</v>
       </c>
       <c r="J633" t="n">
-        <v>22.9614</v>
+        <v>22.9698</v>
       </c>
     </row>
     <row r="634">
@@ -29595,10 +29595,10 @@
         <v>1.44</v>
       </c>
       <c r="I634" t="n">
-        <v>1.006</v>
+        <v>1.0063</v>
       </c>
       <c r="J634" t="n">
-        <v>21.126</v>
+        <v>21.1323</v>
       </c>
     </row>
     <row r="635">
@@ -29635,10 +29635,10 @@
         <v>0.82</v>
       </c>
       <c r="I635" t="n">
-        <v>-0.5878</v>
+        <v>-0.5875</v>
       </c>
       <c r="J635" t="n">
-        <v>-12.3438</v>
+        <v>-12.3375</v>
       </c>
     </row>
     <row r="636">
@@ -29675,10 +29675,10 @@
         <v>0.74</v>
       </c>
       <c r="I636" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.7673</v>
       </c>
       <c r="J636" t="n">
-        <v>-16.1196</v>
+        <v>-16.1133</v>
       </c>
     </row>
     <row r="637">
@@ -29915,10 +29915,10 @@
         <v>2.03</v>
       </c>
       <c r="I642" t="n">
-        <v>1.7276</v>
+        <v>1.7281</v>
       </c>
       <c r="J642" t="n">
-        <v>32.8244</v>
+        <v>32.8339</v>
       </c>
     </row>
     <row r="643">
@@ -29952,13 +29952,13 @@
         <v>19</v>
       </c>
       <c r="H643" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="I643" t="n">
-        <v>1.3532</v>
+        <v>1.3411</v>
       </c>
       <c r="J643" t="n">
-        <v>25.7108</v>
+        <v>25.4809</v>
       </c>
     </row>
     <row r="644">
@@ -29995,10 +29995,10 @@
         <v>1.19</v>
       </c>
       <c r="I644" t="n">
-        <v>0.4965</v>
+        <v>0.4968</v>
       </c>
       <c r="J644" t="n">
-        <v>9.4335</v>
+        <v>9.4392</v>
       </c>
     </row>
     <row r="645">
@@ -30035,10 +30035,10 @@
         <v>1.05</v>
       </c>
       <c r="I645" t="n">
-        <v>0.1382</v>
+        <v>0.1385</v>
       </c>
       <c r="J645" t="n">
-        <v>2.6258</v>
+        <v>2.6315</v>
       </c>
     </row>
     <row r="646">
@@ -30075,10 +30075,10 @@
         <v>0.97</v>
       </c>
       <c r="I646" t="n">
-        <v>-0.2026</v>
+        <v>-0.2023</v>
       </c>
       <c r="J646" t="n">
-        <v>-3.8494</v>
+        <v>-3.8437</v>
       </c>
     </row>
     <row r="647">
@@ -30115,10 +30115,10 @@
         <v>1.14</v>
       </c>
       <c r="I647" t="n">
-        <v>0.4095</v>
+        <v>0.4085</v>
       </c>
       <c r="J647" t="n">
-        <v>7.7805</v>
+        <v>7.7615</v>
       </c>
     </row>
     <row r="648">
@@ -30155,10 +30155,10 @@
         <v>0.87</v>
       </c>
       <c r="I648" t="n">
-        <v>-0.1566</v>
+        <v>-0.1569</v>
       </c>
       <c r="J648" t="n">
-        <v>-2.9754</v>
+        <v>-2.9811</v>
       </c>
     </row>
     <row r="649">
@@ -30195,10 +30195,10 @@
         <v>0.85</v>
       </c>
       <c r="I649" t="n">
-        <v>-0.1786</v>
+        <v>-0.1789</v>
       </c>
       <c r="J649" t="n">
-        <v>-3.3934</v>
+        <v>-3.3991</v>
       </c>
     </row>
     <row r="650">
@@ -30232,13 +30232,13 @@
         <v>19</v>
       </c>
       <c r="H650" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I650" t="n">
-        <v>-0.5179</v>
+        <v>-0.5095</v>
       </c>
       <c r="J650" t="n">
-        <v>-9.8401</v>
+        <v>-9.6805</v>
       </c>
     </row>
     <row r="651">
@@ -30275,10 +30275,10 @@
         <v>0.43</v>
       </c>
       <c r="I651" t="n">
-        <v>-0.5611</v>
+        <v>-0.5613</v>
       </c>
       <c r="J651" t="n">
-        <v>-10.6609</v>
+        <v>-10.6647</v>
       </c>
     </row>
     <row r="652">
@@ -30644,7 +30644,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -30912,13 +30912,13 @@
         <v>16</v>
       </c>
       <c r="H667" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I667" t="n">
-        <v>1.5554</v>
+        <v>1.5436</v>
       </c>
       <c r="J667" t="n">
-        <v>24.8864</v>
+        <v>24.6976</v>
       </c>
     </row>
     <row r="668">
@@ -30955,16 +30955,16 @@
         <v>1.29</v>
       </c>
       <c r="I668" t="n">
-        <v>0.7183</v>
+        <v>0.7185</v>
       </c>
       <c r="J668" t="n">
-        <v>11.4928</v>
+        <v>11.496</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -30995,10 +30995,10 @@
         <v>1.27</v>
       </c>
       <c r="I669" t="n">
-        <v>0.6783</v>
+        <v>0.6786</v>
       </c>
       <c r="J669" t="n">
-        <v>10.8528</v>
+        <v>10.8576</v>
       </c>
     </row>
     <row r="670">
@@ -31035,10 +31035,10 @@
         <v>1.19</v>
       </c>
       <c r="I670" t="n">
-        <v>0.5082</v>
+        <v>0.5085</v>
       </c>
       <c r="J670" t="n">
-        <v>8.1312</v>
+        <v>8.135999999999999</v>
       </c>
     </row>
     <row r="671">
@@ -31075,10 +31075,10 @@
         <v>0.95</v>
       </c>
       <c r="I671" t="n">
-        <v>-0.2564</v>
+        <v>-0.2561</v>
       </c>
       <c r="J671" t="n">
-        <v>-4.1024</v>
+        <v>-4.0976</v>
       </c>
     </row>
   </sheetData>
